--- a/datasets/RAWDATA_GHG.xlsx
+++ b/datasets/RAWDATA_GHG.xlsx
@@ -1419,23 +1419,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1450,6 +1433,23 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1669,7 +1669,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AH995"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -1791,7 +1790,7 @@
       <c r="I2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="28">
+      <c r="J2" s="41">
         <v>43.1</v>
       </c>
       <c r="K2" s="26">
@@ -1800,7 +1799,7 @@
       <c r="L2" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="27">
+      <c r="M2" s="35">
         <v>56100</v>
       </c>
       <c r="N2" s="26">
@@ -1861,13 +1860,13 @@
         <v>2</v>
       </c>
       <c r="H3" s="9">
-        <f t="shared" ref="H2:H13" si="0">E3/$J$2</f>
+        <f t="shared" ref="H3:H13" si="0">E3/$J$2</f>
         <v>23710.150812064963</v>
       </c>
       <c r="I3" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="29"/>
+      <c r="J3" s="37"/>
       <c r="K3" s="24"/>
       <c r="L3" s="24"/>
       <c r="M3" s="24"/>
@@ -1925,7 +1924,7 @@
       <c r="I4" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="29"/>
+      <c r="J4" s="37"/>
       <c r="K4" s="24"/>
       <c r="L4" s="24"/>
       <c r="M4" s="24"/>
@@ -1983,7 +1982,7 @@
       <c r="I5" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="29"/>
+      <c r="J5" s="37"/>
       <c r="K5" s="24"/>
       <c r="L5" s="24"/>
       <c r="M5" s="24"/>
@@ -2041,7 +2040,7 @@
       <c r="I6" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J6" s="29"/>
+      <c r="J6" s="37"/>
       <c r="K6" s="24"/>
       <c r="L6" s="24"/>
       <c r="M6" s="24"/>
@@ -2099,7 +2098,7 @@
       <c r="I7" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J7" s="29"/>
+      <c r="J7" s="37"/>
       <c r="K7" s="24"/>
       <c r="L7" s="24"/>
       <c r="M7" s="24"/>
@@ -2157,7 +2156,7 @@
       <c r="I8" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="29"/>
+      <c r="J8" s="37"/>
       <c r="K8" s="24"/>
       <c r="L8" s="24"/>
       <c r="M8" s="24"/>
@@ -2215,7 +2214,7 @@
       <c r="I9" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="29"/>
+      <c r="J9" s="37"/>
       <c r="K9" s="24"/>
       <c r="L9" s="24"/>
       <c r="M9" s="24"/>
@@ -2273,7 +2272,7 @@
       <c r="I10" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J10" s="29"/>
+      <c r="J10" s="37"/>
       <c r="K10" s="24"/>
       <c r="L10" s="24"/>
       <c r="M10" s="24"/>
@@ -2331,7 +2330,7 @@
       <c r="I11" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="29"/>
+      <c r="J11" s="37"/>
       <c r="K11" s="24"/>
       <c r="L11" s="24"/>
       <c r="M11" s="24"/>
@@ -2389,7 +2388,7 @@
       <c r="I12" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="29"/>
+      <c r="J12" s="37"/>
       <c r="K12" s="24"/>
       <c r="L12" s="24"/>
       <c r="M12" s="24"/>
@@ -2447,7 +2446,7 @@
       <c r="I13" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="30"/>
+      <c r="J13" s="38"/>
       <c r="K13" s="25"/>
       <c r="L13" s="25"/>
       <c r="M13" s="25"/>
@@ -2476,7 +2475,7 @@
       <c r="AG13" s="1"/>
       <c r="AH13" s="1"/>
     </row>
-    <row r="14" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="14" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A14" s="4" t="s">
         <v>27</v>
       </c>
@@ -2514,13 +2513,13 @@
       <c r="L14" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="M14" s="27">
+      <c r="M14" s="35">
         <v>69300</v>
       </c>
-      <c r="N14" s="27">
+      <c r="N14" s="35">
         <v>25</v>
       </c>
-      <c r="O14" s="27">
+      <c r="O14" s="35">
         <v>8</v>
       </c>
       <c r="P14" s="23">
@@ -2552,7 +2551,7 @@
       <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>
     </row>
-    <row r="15" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="15" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A15" s="4" t="s">
         <v>30</v>
       </c>
@@ -2610,7 +2609,7 @@
       <c r="AG15" s="1"/>
       <c r="AH15" s="1"/>
     </row>
-    <row r="16" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="16" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A16" s="4" t="s">
         <v>31</v>
       </c>
@@ -2668,7 +2667,7 @@
       <c r="AG16" s="1"/>
       <c r="AH16" s="1"/>
     </row>
-    <row r="17" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="17" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A17" s="4" t="s">
         <v>32</v>
       </c>
@@ -2726,7 +2725,7 @@
       <c r="AG17" s="1"/>
       <c r="AH17" s="1"/>
     </row>
-    <row r="18" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="18" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A18" s="4" t="s">
         <v>33</v>
       </c>
@@ -2784,7 +2783,7 @@
       <c r="AG18" s="1"/>
       <c r="AH18" s="1"/>
     </row>
-    <row r="19" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="19" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A19" s="4" t="s">
         <v>34</v>
       </c>
@@ -2842,7 +2841,7 @@
       <c r="AG19" s="1"/>
       <c r="AH19" s="1"/>
     </row>
-    <row r="20" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="20" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A20" s="4" t="s">
         <v>35</v>
       </c>
@@ -2900,7 +2899,7 @@
       <c r="AG20" s="1"/>
       <c r="AH20" s="1"/>
     </row>
-    <row r="21" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="21" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A21" s="4" t="s">
         <v>36</v>
       </c>
@@ -2958,7 +2957,7 @@
       <c r="AG21" s="1"/>
       <c r="AH21" s="1"/>
     </row>
-    <row r="22" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="22" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A22" s="4" t="s">
         <v>37</v>
       </c>
@@ -3016,7 +3015,7 @@
       <c r="AG22" s="1"/>
       <c r="AH22" s="1"/>
     </row>
-    <row r="23" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="23" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A23" s="4" t="s">
         <v>38</v>
       </c>
@@ -3074,7 +3073,7 @@
       <c r="AG23" s="1"/>
       <c r="AH23" s="1"/>
     </row>
-    <row r="24" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="24" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A24" s="4" t="s">
         <v>39</v>
       </c>
@@ -3132,7 +3131,7 @@
       <c r="AG24" s="1"/>
       <c r="AH24" s="1"/>
     </row>
-    <row r="25" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="25" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A25" s="4" t="s">
         <v>40</v>
       </c>
@@ -3190,7 +3189,7 @@
       <c r="AG25" s="1"/>
       <c r="AH25" s="1"/>
     </row>
-    <row r="26" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="26" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A26" s="4" t="s">
         <v>41</v>
       </c>
@@ -3226,18 +3225,18 @@
       <c r="L26" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="M26" s="34">
+      <c r="M26" s="27">
         <v>0.2</v>
       </c>
-      <c r="N26" s="34" t="s">
+      <c r="N26" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="O26" s="37">
+      <c r="O26" s="30">
         <v>23900</v>
       </c>
-      <c r="P26" s="40"/>
-      <c r="Q26" s="41"/>
-      <c r="R26" s="41"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="34"/>
+      <c r="R26" s="34"/>
       <c r="S26" s="13">
         <f t="shared" ref="S26:S37" si="5">H26*$K$26*$M$26*$O$26</f>
         <v>111950.94600000001</v>
@@ -3258,7 +3257,7 @@
       <c r="AG26" s="1"/>
       <c r="AH26" s="1"/>
     </row>
-    <row r="27" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="27" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A27" s="4" t="s">
         <v>45</v>
       </c>
@@ -3290,12 +3289,12 @@
       <c r="J27" s="24"/>
       <c r="K27" s="24"/>
       <c r="L27" s="24"/>
-      <c r="M27" s="35"/>
-      <c r="N27" s="35"/>
-      <c r="O27" s="38"/>
-      <c r="P27" s="38"/>
-      <c r="Q27" s="38"/>
-      <c r="R27" s="38"/>
+      <c r="M27" s="28"/>
+      <c r="N27" s="28"/>
+      <c r="O27" s="31"/>
+      <c r="P27" s="31"/>
+      <c r="Q27" s="31"/>
+      <c r="R27" s="31"/>
       <c r="S27" s="13">
         <f t="shared" si="5"/>
         <v>107050.96800000002</v>
@@ -3316,7 +3315,7 @@
       <c r="AG27" s="1"/>
       <c r="AH27" s="1"/>
     </row>
-    <row r="28" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="28" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A28" s="4" t="s">
         <v>46</v>
       </c>
@@ -3348,12 +3347,12 @@
       <c r="J28" s="24"/>
       <c r="K28" s="24"/>
       <c r="L28" s="24"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="35"/>
-      <c r="O28" s="38"/>
-      <c r="P28" s="38"/>
-      <c r="Q28" s="38"/>
-      <c r="R28" s="38"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="31"/>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="31"/>
       <c r="S28" s="13">
         <f t="shared" si="5"/>
         <v>102611.30399999999</v>
@@ -3374,7 +3373,7 @@
       <c r="AG28" s="1"/>
       <c r="AH28" s="1"/>
     </row>
-    <row r="29" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="29" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A29" s="4" t="s">
         <v>47</v>
       </c>
@@ -3406,12 +3405,12 @@
       <c r="J29" s="24"/>
       <c r="K29" s="24"/>
       <c r="L29" s="24"/>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="38"/>
-      <c r="P29" s="38"/>
-      <c r="Q29" s="38"/>
-      <c r="R29" s="38"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
       <c r="S29" s="13">
         <f t="shared" si="5"/>
         <v>112015.47600000001</v>
@@ -3432,7 +3431,7 @@
       <c r="AG29" s="1"/>
       <c r="AH29" s="1"/>
     </row>
-    <row r="30" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="30" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A30" s="4" t="s">
         <v>48</v>
       </c>
@@ -3464,12 +3463,12 @@
       <c r="J30" s="24"/>
       <c r="K30" s="24"/>
       <c r="L30" s="24"/>
-      <c r="M30" s="35"/>
-      <c r="N30" s="35"/>
-      <c r="O30" s="38"/>
-      <c r="P30" s="38"/>
-      <c r="Q30" s="38"/>
-      <c r="R30" s="38"/>
+      <c r="M30" s="28"/>
+      <c r="N30" s="28"/>
+      <c r="O30" s="31"/>
+      <c r="P30" s="31"/>
+      <c r="Q30" s="31"/>
+      <c r="R30" s="31"/>
       <c r="S30" s="13">
         <f t="shared" si="5"/>
         <v>98717.994000000006</v>
@@ -3490,7 +3489,7 @@
       <c r="AG30" s="1"/>
       <c r="AH30" s="1"/>
     </row>
-    <row r="31" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="31" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A31" s="4" t="s">
         <v>49</v>
       </c>
@@ -3522,12 +3521,12 @@
       <c r="J31" s="24"/>
       <c r="K31" s="24"/>
       <c r="L31" s="24"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="38"/>
-      <c r="P31" s="38"/>
-      <c r="Q31" s="38"/>
-      <c r="R31" s="38"/>
+      <c r="M31" s="28"/>
+      <c r="N31" s="28"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="31"/>
+      <c r="Q31" s="31"/>
+      <c r="R31" s="31"/>
       <c r="S31" s="13">
         <f t="shared" si="5"/>
         <v>116812.20600000001</v>
@@ -3548,7 +3547,7 @@
       <c r="AG31" s="1"/>
       <c r="AH31" s="1"/>
     </row>
-    <row r="32" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="32" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A32" s="4" t="s">
         <v>50</v>
       </c>
@@ -3580,12 +3579,12 @@
       <c r="J32" s="24"/>
       <c r="K32" s="24"/>
       <c r="L32" s="24"/>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
-      <c r="O32" s="38"/>
-      <c r="P32" s="38"/>
-      <c r="Q32" s="38"/>
-      <c r="R32" s="38"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
       <c r="S32" s="13">
         <f t="shared" si="5"/>
         <v>104420.29500000001</v>
@@ -3606,7 +3605,7 @@
       <c r="AG32" s="1"/>
       <c r="AH32" s="1"/>
     </row>
-    <row r="33" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="33" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A33" s="4" t="s">
         <v>51</v>
       </c>
@@ -3638,12 +3637,12 @@
       <c r="J33" s="24"/>
       <c r="K33" s="24"/>
       <c r="L33" s="24"/>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
-      <c r="O33" s="38"/>
-      <c r="P33" s="38"/>
-      <c r="Q33" s="38"/>
-      <c r="R33" s="38"/>
+      <c r="M33" s="28"/>
+      <c r="N33" s="28"/>
+      <c r="O33" s="31"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="31"/>
       <c r="S33" s="13">
         <f t="shared" si="5"/>
         <v>111120.66</v>
@@ -3664,7 +3663,7 @@
       <c r="AG33" s="1"/>
       <c r="AH33" s="1"/>
     </row>
-    <row r="34" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="34" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A34" s="4" t="s">
         <v>52</v>
       </c>
@@ -3696,12 +3695,12 @@
       <c r="J34" s="24"/>
       <c r="K34" s="24"/>
       <c r="L34" s="24"/>
-      <c r="M34" s="35"/>
-      <c r="N34" s="35"/>
-      <c r="O34" s="38"/>
-      <c r="P34" s="38"/>
-      <c r="Q34" s="38"/>
-      <c r="R34" s="38"/>
+      <c r="M34" s="28"/>
+      <c r="N34" s="28"/>
+      <c r="O34" s="31"/>
+      <c r="P34" s="31"/>
+      <c r="Q34" s="31"/>
+      <c r="R34" s="31"/>
       <c r="S34" s="13">
         <f t="shared" si="5"/>
         <v>98446.968000000008</v>
@@ -3722,7 +3721,7 @@
       <c r="AG34" s="1"/>
       <c r="AH34" s="1"/>
     </row>
-    <row r="35" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="35" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A35" s="4" t="s">
         <v>53</v>
       </c>
@@ -3754,12 +3753,12 @@
       <c r="J35" s="24"/>
       <c r="K35" s="24"/>
       <c r="L35" s="24"/>
-      <c r="M35" s="35"/>
-      <c r="N35" s="35"/>
-      <c r="O35" s="38"/>
-      <c r="P35" s="38"/>
-      <c r="Q35" s="38"/>
-      <c r="R35" s="38"/>
+      <c r="M35" s="28"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="31"/>
+      <c r="P35" s="31"/>
+      <c r="Q35" s="31"/>
+      <c r="R35" s="31"/>
       <c r="S35" s="13">
         <f t="shared" si="5"/>
         <v>108406.098</v>
@@ -3780,7 +3779,7 @@
       <c r="AG35" s="1"/>
       <c r="AH35" s="1"/>
     </row>
-    <row r="36" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="36" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A36" s="4" t="s">
         <v>54</v>
       </c>
@@ -3812,12 +3811,12 @@
       <c r="J36" s="24"/>
       <c r="K36" s="24"/>
       <c r="L36" s="24"/>
-      <c r="M36" s="35"/>
-      <c r="N36" s="35"/>
-      <c r="O36" s="38"/>
-      <c r="P36" s="38"/>
-      <c r="Q36" s="38"/>
-      <c r="R36" s="38"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="31"/>
+      <c r="P36" s="31"/>
+      <c r="Q36" s="31"/>
+      <c r="R36" s="31"/>
       <c r="S36" s="13">
         <f t="shared" si="5"/>
         <v>101413.19699999999</v>
@@ -3838,7 +3837,7 @@
       <c r="AG36" s="1"/>
       <c r="AH36" s="1"/>
     </row>
-    <row r="37" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="37" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A37" s="4" t="s">
         <v>55</v>
       </c>
@@ -3870,12 +3869,12 @@
       <c r="J37" s="25"/>
       <c r="K37" s="25"/>
       <c r="L37" s="25"/>
-      <c r="M37" s="36"/>
-      <c r="N37" s="35"/>
-      <c r="O37" s="39"/>
-      <c r="P37" s="38"/>
-      <c r="Q37" s="38"/>
-      <c r="R37" s="38"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="31"/>
       <c r="S37" s="13">
         <f t="shared" si="5"/>
         <v>113592.159</v>
@@ -3896,7 +3895,7 @@
       <c r="AG37" s="1"/>
       <c r="AH37" s="1"/>
     </row>
-    <row r="38" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="38" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A38" s="4" t="s">
         <v>56</v>
       </c>
@@ -3932,18 +3931,18 @@
       <c r="L38" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="M38" s="34">
+      <c r="M38" s="27">
         <v>0.4</v>
       </c>
-      <c r="N38" s="34" t="s">
+      <c r="N38" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="O38" s="37">
+      <c r="O38" s="30">
         <v>11700</v>
       </c>
-      <c r="P38" s="40"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="41"/>
+      <c r="P38" s="33"/>
+      <c r="Q38" s="34"/>
+      <c r="R38" s="34"/>
       <c r="S38" s="7">
         <f t="shared" ref="S38:S49" si="6">H38*$K$38*$M$38*$O$38</f>
         <v>4664.79</v>
@@ -3964,7 +3963,7 @@
       <c r="AG38" s="1"/>
       <c r="AH38" s="1"/>
     </row>
-    <row r="39" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="39" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A39" s="4" t="s">
         <v>57</v>
       </c>
@@ -3996,12 +3995,12 @@
       <c r="J39" s="24"/>
       <c r="K39" s="24"/>
       <c r="L39" s="24"/>
-      <c r="M39" s="35"/>
-      <c r="N39" s="35"/>
-      <c r="O39" s="38"/>
-      <c r="P39" s="38"/>
-      <c r="Q39" s="38"/>
-      <c r="R39" s="38"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="31"/>
+      <c r="P39" s="31"/>
+      <c r="Q39" s="31"/>
+      <c r="R39" s="31"/>
       <c r="S39" s="7">
         <f t="shared" si="6"/>
         <v>4628.9880000000003</v>
@@ -4022,7 +4021,7 @@
       <c r="AG39" s="1"/>
       <c r="AH39" s="1"/>
     </row>
-    <row r="40" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="40" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A40" s="4" t="s">
         <v>58</v>
       </c>
@@ -4054,12 +4053,12 @@
       <c r="J40" s="24"/>
       <c r="K40" s="24"/>
       <c r="L40" s="24"/>
-      <c r="M40" s="35"/>
-      <c r="N40" s="35"/>
-      <c r="O40" s="38"/>
-      <c r="P40" s="38"/>
-      <c r="Q40" s="38"/>
-      <c r="R40" s="38"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="31"/>
+      <c r="R40" s="31"/>
       <c r="S40" s="7">
         <f t="shared" si="6"/>
         <v>4445.7660000000005</v>
@@ -4080,7 +4079,7 @@
       <c r="AG40" s="1"/>
       <c r="AH40" s="1"/>
     </row>
-    <row r="41" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="41" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A41" s="4" t="s">
         <v>59</v>
       </c>
@@ -4112,12 +4111,12 @@
       <c r="J41" s="24"/>
       <c r="K41" s="24"/>
       <c r="L41" s="24"/>
-      <c r="M41" s="35"/>
-      <c r="N41" s="35"/>
-      <c r="O41" s="38"/>
-      <c r="P41" s="38"/>
-      <c r="Q41" s="38"/>
-      <c r="R41" s="38"/>
+      <c r="M41" s="28"/>
+      <c r="N41" s="28"/>
+      <c r="O41" s="31"/>
+      <c r="P41" s="31"/>
+      <c r="Q41" s="31"/>
+      <c r="R41" s="31"/>
       <c r="S41" s="7">
         <f t="shared" si="6"/>
         <v>4178.304000000001</v>
@@ -4138,7 +4137,7 @@
       <c r="AG41" s="1"/>
       <c r="AH41" s="1"/>
     </row>
-    <row r="42" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="42" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A42" s="4" t="s">
         <v>60</v>
       </c>
@@ -4170,12 +4169,12 @@
       <c r="J42" s="24"/>
       <c r="K42" s="24"/>
       <c r="L42" s="24"/>
-      <c r="M42" s="35"/>
-      <c r="N42" s="35"/>
-      <c r="O42" s="38"/>
-      <c r="P42" s="38"/>
-      <c r="Q42" s="38"/>
-      <c r="R42" s="38"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="31"/>
+      <c r="P42" s="31"/>
+      <c r="Q42" s="31"/>
+      <c r="R42" s="31"/>
       <c r="S42" s="7">
         <f t="shared" si="6"/>
         <v>4576.3380000000006</v>
@@ -4196,7 +4195,7 @@
       <c r="AG42" s="1"/>
       <c r="AH42" s="1"/>
     </row>
-    <row r="43" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="43" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A43" s="4" t="s">
         <v>61</v>
       </c>
@@ -4228,12 +4227,12 @@
       <c r="J43" s="24"/>
       <c r="K43" s="24"/>
       <c r="L43" s="24"/>
-      <c r="M43" s="35"/>
-      <c r="N43" s="35"/>
-      <c r="O43" s="38"/>
-      <c r="P43" s="38"/>
-      <c r="Q43" s="38"/>
-      <c r="R43" s="38"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+      <c r="R43" s="31"/>
       <c r="S43" s="7">
         <f t="shared" si="6"/>
         <v>4245.6960000000008</v>
@@ -4254,7 +4253,7 @@
       <c r="AG43" s="1"/>
       <c r="AH43" s="1"/>
     </row>
-    <row r="44" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="44" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A44" s="4" t="s">
         <v>62</v>
       </c>
@@ -4286,12 +4285,12 @@
       <c r="J44" s="24"/>
       <c r="K44" s="24"/>
       <c r="L44" s="24"/>
-      <c r="M44" s="35"/>
-      <c r="N44" s="35"/>
-      <c r="O44" s="38"/>
-      <c r="P44" s="38"/>
-      <c r="Q44" s="38"/>
-      <c r="R44" s="38"/>
+      <c r="M44" s="28"/>
+      <c r="N44" s="28"/>
+      <c r="O44" s="31"/>
+      <c r="P44" s="31"/>
+      <c r="Q44" s="31"/>
+      <c r="R44" s="31"/>
       <c r="S44" s="7">
         <f t="shared" si="6"/>
         <v>4643.7300000000005</v>
@@ -4312,7 +4311,7 @@
       <c r="AG44" s="1"/>
       <c r="AH44" s="1"/>
     </row>
-    <row r="45" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="45" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A45" s="4" t="s">
         <v>63</v>
       </c>
@@ -4344,12 +4343,12 @@
       <c r="J45" s="24"/>
       <c r="K45" s="24"/>
       <c r="L45" s="24"/>
-      <c r="M45" s="35"/>
-      <c r="N45" s="35"/>
-      <c r="O45" s="38"/>
-      <c r="P45" s="38"/>
-      <c r="Q45" s="38"/>
-      <c r="R45" s="38"/>
+      <c r="M45" s="28"/>
+      <c r="N45" s="28"/>
+      <c r="O45" s="31"/>
+      <c r="P45" s="31"/>
+      <c r="Q45" s="31"/>
+      <c r="R45" s="31"/>
       <c r="S45" s="7">
         <f t="shared" si="6"/>
         <v>4588.9740000000002</v>
@@ -4370,7 +4369,7 @@
       <c r="AG45" s="1"/>
       <c r="AH45" s="1"/>
     </row>
-    <row r="46" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="46" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A46" s="4" t="s">
         <v>64</v>
       </c>
@@ -4402,12 +4401,12 @@
       <c r="J46" s="24"/>
       <c r="K46" s="24"/>
       <c r="L46" s="24"/>
-      <c r="M46" s="35"/>
-      <c r="N46" s="35"/>
-      <c r="O46" s="38"/>
-      <c r="P46" s="38"/>
-      <c r="Q46" s="38"/>
-      <c r="R46" s="38"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="28"/>
+      <c r="O46" s="31"/>
+      <c r="P46" s="31"/>
+      <c r="Q46" s="31"/>
+      <c r="R46" s="31"/>
       <c r="S46" s="7">
         <f t="shared" si="6"/>
         <v>4110.9120000000003</v>
@@ -4428,7 +4427,7 @@
       <c r="AG46" s="1"/>
       <c r="AH46" s="1"/>
     </row>
-    <row r="47" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="47" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A47" s="4" t="s">
         <v>65</v>
       </c>
@@ -4460,12 +4459,12 @@
       <c r="J47" s="24"/>
       <c r="K47" s="24"/>
       <c r="L47" s="24"/>
-      <c r="M47" s="35"/>
-      <c r="N47" s="35"/>
-      <c r="O47" s="38"/>
-      <c r="P47" s="38"/>
-      <c r="Q47" s="38"/>
-      <c r="R47" s="38"/>
+      <c r="M47" s="28"/>
+      <c r="N47" s="28"/>
+      <c r="O47" s="31"/>
+      <c r="P47" s="31"/>
+      <c r="Q47" s="31"/>
+      <c r="R47" s="31"/>
       <c r="S47" s="7">
         <f t="shared" si="6"/>
         <v>4508.9460000000008</v>
@@ -4486,7 +4485,7 @@
       <c r="AG47" s="1"/>
       <c r="AH47" s="1"/>
     </row>
-    <row r="48" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="48" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A48" s="4" t="s">
         <v>66</v>
       </c>
@@ -4518,12 +4517,12 @@
       <c r="J48" s="24"/>
       <c r="K48" s="24"/>
       <c r="L48" s="24"/>
-      <c r="M48" s="35"/>
-      <c r="N48" s="35"/>
-      <c r="O48" s="38"/>
-      <c r="P48" s="38"/>
-      <c r="Q48" s="38"/>
-      <c r="R48" s="38"/>
+      <c r="M48" s="28"/>
+      <c r="N48" s="28"/>
+      <c r="O48" s="31"/>
+      <c r="P48" s="31"/>
+      <c r="Q48" s="31"/>
+      <c r="R48" s="31"/>
       <c r="S48" s="7">
         <f t="shared" si="6"/>
         <v>4338.3600000000006</v>
@@ -4544,7 +4543,7 @@
       <c r="AG48" s="1"/>
       <c r="AH48" s="1"/>
     </row>
-    <row r="49" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="49" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A49" s="4" t="s">
         <v>67</v>
       </c>
@@ -4576,12 +4575,12 @@
       <c r="J49" s="25"/>
       <c r="K49" s="25"/>
       <c r="L49" s="25"/>
-      <c r="M49" s="36"/>
-      <c r="N49" s="35"/>
-      <c r="O49" s="39"/>
-      <c r="P49" s="38"/>
-      <c r="Q49" s="38"/>
-      <c r="R49" s="38"/>
+      <c r="M49" s="29"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="32"/>
+      <c r="P49" s="31"/>
+      <c r="Q49" s="31"/>
+      <c r="R49" s="31"/>
       <c r="S49" s="7">
         <f t="shared" si="6"/>
         <v>4669.0020000000004</v>
@@ -4602,7 +4601,7 @@
       <c r="AG49" s="1"/>
       <c r="AH49" s="1"/>
     </row>
-    <row r="50" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="50" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A50" s="4" t="s">
         <v>68</v>
       </c>
@@ -4676,7 +4675,7 @@
       <c r="AG50" s="1"/>
       <c r="AH50" s="1"/>
     </row>
-    <row r="51" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="51" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A51" s="4" t="s">
         <v>71</v>
       </c>
@@ -4734,7 +4733,7 @@
       <c r="AG51" s="1"/>
       <c r="AH51" s="1"/>
     </row>
-    <row r="52" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="52" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A52" s="4" t="s">
         <v>72</v>
       </c>
@@ -4792,7 +4791,7 @@
       <c r="AG52" s="1"/>
       <c r="AH52" s="1"/>
     </row>
-    <row r="53" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="53" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A53" s="4" t="s">
         <v>73</v>
       </c>
@@ -4850,7 +4849,7 @@
       <c r="AG53" s="1"/>
       <c r="AH53" s="1"/>
     </row>
-    <row r="54" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="54" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A54" s="4" t="s">
         <v>74</v>
       </c>
@@ -4908,7 +4907,7 @@
       <c r="AG54" s="1"/>
       <c r="AH54" s="1"/>
     </row>
-    <row r="55" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="55" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A55" s="4" t="s">
         <v>75</v>
       </c>
@@ -4966,7 +4965,7 @@
       <c r="AG55" s="1"/>
       <c r="AH55" s="1"/>
     </row>
-    <row r="56" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="56" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A56" s="4" t="s">
         <v>76</v>
       </c>
@@ -5024,7 +5023,7 @@
       <c r="AG56" s="1"/>
       <c r="AH56" s="1"/>
     </row>
-    <row r="57" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="57" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A57" s="4" t="s">
         <v>77</v>
       </c>
@@ -5082,7 +5081,7 @@
       <c r="AG57" s="1"/>
       <c r="AH57" s="1"/>
     </row>
-    <row r="58" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="58" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A58" s="4" t="s">
         <v>78</v>
       </c>
@@ -5140,7 +5139,7 @@
       <c r="AG58" s="1"/>
       <c r="AH58" s="1"/>
     </row>
-    <row r="59" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="59" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A59" s="4" t="s">
         <v>79</v>
       </c>
@@ -5198,7 +5197,7 @@
       <c r="AG59" s="1"/>
       <c r="AH59" s="1"/>
     </row>
-    <row r="60" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="60" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A60" s="4" t="s">
         <v>80</v>
       </c>
@@ -5256,7 +5255,7 @@
       <c r="AG60" s="1"/>
       <c r="AH60" s="1"/>
     </row>
-    <row r="61" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="61" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A61" s="4" t="s">
         <v>81</v>
       </c>
@@ -5314,7 +5313,7 @@
       <c r="AG61" s="1"/>
       <c r="AH61" s="1"/>
     </row>
-    <row r="62" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="62" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A62" s="4" t="s">
         <v>82</v>
       </c>
@@ -5346,13 +5345,13 @@
       <c r="J62" s="26"/>
       <c r="K62" s="26"/>
       <c r="L62" s="26"/>
-      <c r="M62" s="31">
+      <c r="M62" s="36">
         <v>59510</v>
       </c>
-      <c r="N62" s="32">
+      <c r="N62" s="39">
         <v>1.8320000000000001</v>
       </c>
-      <c r="O62" s="33">
+      <c r="O62" s="40">
         <v>0.44</v>
       </c>
       <c r="P62" s="23">
@@ -5384,7 +5383,7 @@
       <c r="AG62" s="1"/>
       <c r="AH62" s="1"/>
     </row>
-    <row r="63" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="63" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A63" s="15" t="s">
         <v>85</v>
       </c>
@@ -5416,8 +5415,8 @@
       <c r="J63" s="24"/>
       <c r="K63" s="24"/>
       <c r="L63" s="24"/>
-      <c r="M63" s="29"/>
-      <c r="N63" s="29"/>
+      <c r="M63" s="37"/>
+      <c r="N63" s="37"/>
       <c r="O63" s="24"/>
       <c r="P63" s="24"/>
       <c r="Q63" s="24"/>
@@ -5442,7 +5441,7 @@
       <c r="AG63" s="1"/>
       <c r="AH63" s="1"/>
     </row>
-    <row r="64" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="64" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A64" s="15" t="s">
         <v>86</v>
       </c>
@@ -5474,8 +5473,8 @@
       <c r="J64" s="24"/>
       <c r="K64" s="24"/>
       <c r="L64" s="24"/>
-      <c r="M64" s="29"/>
-      <c r="N64" s="29"/>
+      <c r="M64" s="37"/>
+      <c r="N64" s="37"/>
       <c r="O64" s="24"/>
       <c r="P64" s="24"/>
       <c r="Q64" s="24"/>
@@ -5500,7 +5499,7 @@
       <c r="AG64" s="1"/>
       <c r="AH64" s="1"/>
     </row>
-    <row r="65" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="65" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A65" s="15" t="s">
         <v>87</v>
       </c>
@@ -5532,8 +5531,8 @@
       <c r="J65" s="24"/>
       <c r="K65" s="24"/>
       <c r="L65" s="24"/>
-      <c r="M65" s="29"/>
-      <c r="N65" s="29"/>
+      <c r="M65" s="37"/>
+      <c r="N65" s="37"/>
       <c r="O65" s="24"/>
       <c r="P65" s="24"/>
       <c r="Q65" s="24"/>
@@ -5558,7 +5557,7 @@
       <c r="AG65" s="1"/>
       <c r="AH65" s="1"/>
     </row>
-    <row r="66" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="66" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A66" s="15" t="s">
         <v>88</v>
       </c>
@@ -5590,8 +5589,8 @@
       <c r="J66" s="24"/>
       <c r="K66" s="24"/>
       <c r="L66" s="24"/>
-      <c r="M66" s="29"/>
-      <c r="N66" s="29"/>
+      <c r="M66" s="37"/>
+      <c r="N66" s="37"/>
       <c r="O66" s="24"/>
       <c r="P66" s="24"/>
       <c r="Q66" s="24"/>
@@ -5616,7 +5615,7 @@
       <c r="AG66" s="1"/>
       <c r="AH66" s="1"/>
     </row>
-    <row r="67" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="67" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A67" s="15" t="s">
         <v>89</v>
       </c>
@@ -5648,8 +5647,8 @@
       <c r="J67" s="24"/>
       <c r="K67" s="24"/>
       <c r="L67" s="24"/>
-      <c r="M67" s="29"/>
-      <c r="N67" s="29"/>
+      <c r="M67" s="37"/>
+      <c r="N67" s="37"/>
       <c r="O67" s="24"/>
       <c r="P67" s="24"/>
       <c r="Q67" s="24"/>
@@ -5674,7 +5673,7 @@
       <c r="AG67" s="1"/>
       <c r="AH67" s="1"/>
     </row>
-    <row r="68" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="68" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A68" s="15" t="s">
         <v>90</v>
       </c>
@@ -5706,8 +5705,8 @@
       <c r="J68" s="24"/>
       <c r="K68" s="24"/>
       <c r="L68" s="24"/>
-      <c r="M68" s="29"/>
-      <c r="N68" s="29"/>
+      <c r="M68" s="37"/>
+      <c r="N68" s="37"/>
       <c r="O68" s="24"/>
       <c r="P68" s="24"/>
       <c r="Q68" s="24"/>
@@ -5732,7 +5731,7 @@
       <c r="AG68" s="1"/>
       <c r="AH68" s="1"/>
     </row>
-    <row r="69" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="69" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A69" s="15" t="s">
         <v>91</v>
       </c>
@@ -5764,8 +5763,8 @@
       <c r="J69" s="24"/>
       <c r="K69" s="24"/>
       <c r="L69" s="24"/>
-      <c r="M69" s="29"/>
-      <c r="N69" s="29"/>
+      <c r="M69" s="37"/>
+      <c r="N69" s="37"/>
       <c r="O69" s="24"/>
       <c r="P69" s="24"/>
       <c r="Q69" s="24"/>
@@ -5790,7 +5789,7 @@
       <c r="AG69" s="1"/>
       <c r="AH69" s="1"/>
     </row>
-    <row r="70" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="70" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A70" s="15" t="s">
         <v>92</v>
       </c>
@@ -5822,8 +5821,8 @@
       <c r="J70" s="24"/>
       <c r="K70" s="24"/>
       <c r="L70" s="24"/>
-      <c r="M70" s="29"/>
-      <c r="N70" s="29"/>
+      <c r="M70" s="37"/>
+      <c r="N70" s="37"/>
       <c r="O70" s="24"/>
       <c r="P70" s="24"/>
       <c r="Q70" s="24"/>
@@ -5848,7 +5847,7 @@
       <c r="AG70" s="1"/>
       <c r="AH70" s="1"/>
     </row>
-    <row r="71" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="71" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A71" s="15" t="s">
         <v>93</v>
       </c>
@@ -5880,8 +5879,8 @@
       <c r="J71" s="24"/>
       <c r="K71" s="24"/>
       <c r="L71" s="24"/>
-      <c r="M71" s="29"/>
-      <c r="N71" s="29"/>
+      <c r="M71" s="37"/>
+      <c r="N71" s="37"/>
       <c r="O71" s="24"/>
       <c r="P71" s="24"/>
       <c r="Q71" s="24"/>
@@ -5906,7 +5905,7 @@
       <c r="AG71" s="1"/>
       <c r="AH71" s="1"/>
     </row>
-    <row r="72" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="72" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A72" s="15" t="s">
         <v>94</v>
       </c>
@@ -5938,8 +5937,8 @@
       <c r="J72" s="24"/>
       <c r="K72" s="24"/>
       <c r="L72" s="24"/>
-      <c r="M72" s="29"/>
-      <c r="N72" s="29"/>
+      <c r="M72" s="37"/>
+      <c r="N72" s="37"/>
       <c r="O72" s="24"/>
       <c r="P72" s="24"/>
       <c r="Q72" s="24"/>
@@ -5964,7 +5963,7 @@
       <c r="AG72" s="1"/>
       <c r="AH72" s="1"/>
     </row>
-    <row r="73" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="73" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A73" s="15" t="s">
         <v>95</v>
       </c>
@@ -5996,8 +5995,8 @@
       <c r="J73" s="25"/>
       <c r="K73" s="25"/>
       <c r="L73" s="25"/>
-      <c r="M73" s="30"/>
-      <c r="N73" s="30"/>
+      <c r="M73" s="38"/>
+      <c r="N73" s="38"/>
       <c r="O73" s="25"/>
       <c r="P73" s="25"/>
       <c r="Q73" s="25"/>
@@ -6051,7 +6050,7 @@
       <c r="I74" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J74" s="28">
+      <c r="J74" s="41">
         <v>43.1</v>
       </c>
       <c r="K74" s="26">
@@ -6060,7 +6059,7 @@
       <c r="L74" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="M74" s="27">
+      <c r="M74" s="35">
         <v>56100</v>
       </c>
       <c r="N74" s="26">
@@ -6127,7 +6126,7 @@
       <c r="I75" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J75" s="29"/>
+      <c r="J75" s="37"/>
       <c r="K75" s="24"/>
       <c r="L75" s="24"/>
       <c r="M75" s="24"/>
@@ -6185,7 +6184,7 @@
       <c r="I76" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J76" s="29"/>
+      <c r="J76" s="37"/>
       <c r="K76" s="24"/>
       <c r="L76" s="24"/>
       <c r="M76" s="24"/>
@@ -6243,7 +6242,7 @@
       <c r="I77" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J77" s="29"/>
+      <c r="J77" s="37"/>
       <c r="K77" s="24"/>
       <c r="L77" s="24"/>
       <c r="M77" s="24"/>
@@ -6301,7 +6300,7 @@
       <c r="I78" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J78" s="29"/>
+      <c r="J78" s="37"/>
       <c r="K78" s="24"/>
       <c r="L78" s="24"/>
       <c r="M78" s="24"/>
@@ -6359,7 +6358,7 @@
       <c r="I79" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J79" s="29"/>
+      <c r="J79" s="37"/>
       <c r="K79" s="24"/>
       <c r="L79" s="24"/>
       <c r="M79" s="24"/>
@@ -6417,7 +6416,7 @@
       <c r="I80" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J80" s="29"/>
+      <c r="J80" s="37"/>
       <c r="K80" s="24"/>
       <c r="L80" s="24"/>
       <c r="M80" s="24"/>
@@ -6475,7 +6474,7 @@
       <c r="I81" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J81" s="29"/>
+      <c r="J81" s="37"/>
       <c r="K81" s="24"/>
       <c r="L81" s="24"/>
       <c r="M81" s="24"/>
@@ -6533,7 +6532,7 @@
       <c r="I82" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J82" s="29"/>
+      <c r="J82" s="37"/>
       <c r="K82" s="24"/>
       <c r="L82" s="24"/>
       <c r="M82" s="24"/>
@@ -6591,7 +6590,7 @@
       <c r="I83" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J83" s="29"/>
+      <c r="J83" s="37"/>
       <c r="K83" s="24"/>
       <c r="L83" s="24"/>
       <c r="M83" s="24"/>
@@ -6649,7 +6648,7 @@
       <c r="I84" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J84" s="29"/>
+      <c r="J84" s="37"/>
       <c r="K84" s="24"/>
       <c r="L84" s="24"/>
       <c r="M84" s="24"/>
@@ -6707,7 +6706,7 @@
       <c r="I85" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J85" s="30"/>
+      <c r="J85" s="38"/>
       <c r="K85" s="25"/>
       <c r="L85" s="25"/>
       <c r="M85" s="25"/>
@@ -6736,7 +6735,7 @@
       <c r="AG85" s="1"/>
       <c r="AH85" s="1"/>
     </row>
-    <row r="86" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="86" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A86" s="4" t="s">
         <v>108</v>
       </c>
@@ -6774,13 +6773,13 @@
       <c r="L86" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="M86" s="27">
+      <c r="M86" s="35">
         <v>69300</v>
       </c>
-      <c r="N86" s="27">
+      <c r="N86" s="35">
         <v>25</v>
       </c>
-      <c r="O86" s="27">
+      <c r="O86" s="35">
         <v>8</v>
       </c>
       <c r="P86" s="23">
@@ -6812,7 +6811,7 @@
       <c r="AG86" s="1"/>
       <c r="AH86" s="1"/>
     </row>
-    <row r="87" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="87" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A87" s="4" t="s">
         <v>109</v>
       </c>
@@ -6870,7 +6869,7 @@
       <c r="AG87" s="1"/>
       <c r="AH87" s="1"/>
     </row>
-    <row r="88" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="88" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A88" s="4" t="s">
         <v>110</v>
       </c>
@@ -6928,7 +6927,7 @@
       <c r="AG88" s="1"/>
       <c r="AH88" s="1"/>
     </row>
-    <row r="89" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="89" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A89" s="4" t="s">
         <v>111</v>
       </c>
@@ -6986,7 +6985,7 @@
       <c r="AG89" s="1"/>
       <c r="AH89" s="1"/>
     </row>
-    <row r="90" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="90" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A90" s="4" t="s">
         <v>112</v>
       </c>
@@ -7044,7 +7043,7 @@
       <c r="AG90" s="1"/>
       <c r="AH90" s="1"/>
     </row>
-    <row r="91" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="91" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A91" s="4" t="s">
         <v>113</v>
       </c>
@@ -7102,7 +7101,7 @@
       <c r="AG91" s="1"/>
       <c r="AH91" s="1"/>
     </row>
-    <row r="92" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="92" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A92" s="4" t="s">
         <v>114</v>
       </c>
@@ -7160,7 +7159,7 @@
       <c r="AG92" s="1"/>
       <c r="AH92" s="1"/>
     </row>
-    <row r="93" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="93" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A93" s="4" t="s">
         <v>115</v>
       </c>
@@ -7218,7 +7217,7 @@
       <c r="AG93" s="1"/>
       <c r="AH93" s="1"/>
     </row>
-    <row r="94" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="94" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A94" s="4" t="s">
         <v>116</v>
       </c>
@@ -7276,7 +7275,7 @@
       <c r="AG94" s="1"/>
       <c r="AH94" s="1"/>
     </row>
-    <row r="95" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="95" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A95" s="4" t="s">
         <v>117</v>
       </c>
@@ -7334,7 +7333,7 @@
       <c r="AG95" s="1"/>
       <c r="AH95" s="1"/>
     </row>
-    <row r="96" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="96" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A96" s="4" t="s">
         <v>118</v>
       </c>
@@ -7392,7 +7391,7 @@
       <c r="AG96" s="1"/>
       <c r="AH96" s="1"/>
     </row>
-    <row r="97" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="97" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A97" s="4" t="s">
         <v>119</v>
       </c>
@@ -7450,7 +7449,7 @@
       <c r="AG97" s="1"/>
       <c r="AH97" s="1"/>
     </row>
-    <row r="98" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="98" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A98" s="4" t="s">
         <v>120</v>
       </c>
@@ -7486,18 +7485,18 @@
       <c r="L98" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="M98" s="34">
+      <c r="M98" s="27">
         <v>0.2</v>
       </c>
-      <c r="N98" s="34" t="s">
+      <c r="N98" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="O98" s="37">
+      <c r="O98" s="30">
         <v>23900</v>
       </c>
-      <c r="P98" s="40"/>
-      <c r="Q98" s="41"/>
-      <c r="R98" s="41"/>
+      <c r="P98" s="33"/>
+      <c r="Q98" s="34"/>
+      <c r="R98" s="34"/>
       <c r="S98" s="13">
         <f t="shared" ref="S98:S109" si="16">H98*$K$98*$M$98*$O$98</f>
         <v>104620.338</v>
@@ -7518,7 +7517,7 @@
       <c r="AG98" s="1"/>
       <c r="AH98" s="1"/>
     </row>
-    <row r="99" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="99" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A99" s="4" t="s">
         <v>121</v>
       </c>
@@ -7550,12 +7549,12 @@
       <c r="J99" s="24"/>
       <c r="K99" s="24"/>
       <c r="L99" s="24"/>
-      <c r="M99" s="35"/>
-      <c r="N99" s="35"/>
-      <c r="O99" s="38"/>
-      <c r="P99" s="38"/>
-      <c r="Q99" s="38"/>
-      <c r="R99" s="38"/>
+      <c r="M99" s="28"/>
+      <c r="N99" s="28"/>
+      <c r="O99" s="31"/>
+      <c r="P99" s="31"/>
+      <c r="Q99" s="31"/>
+      <c r="R99" s="31"/>
       <c r="S99" s="13">
         <f t="shared" si="16"/>
         <v>98094.203999999998</v>
@@ -7576,7 +7575,7 @@
       <c r="AG99" s="1"/>
       <c r="AH99" s="1"/>
     </row>
-    <row r="100" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="100" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A100" s="4" t="s">
         <v>122</v>
       </c>
@@ -7608,12 +7607,12 @@
       <c r="J100" s="24"/>
       <c r="K100" s="24"/>
       <c r="L100" s="24"/>
-      <c r="M100" s="35"/>
-      <c r="N100" s="35"/>
-      <c r="O100" s="38"/>
-      <c r="P100" s="38"/>
-      <c r="Q100" s="38"/>
-      <c r="R100" s="38"/>
+      <c r="M100" s="28"/>
+      <c r="N100" s="28"/>
+      <c r="O100" s="31"/>
+      <c r="P100" s="31"/>
+      <c r="Q100" s="31"/>
+      <c r="R100" s="31"/>
       <c r="S100" s="13">
         <f t="shared" si="16"/>
         <v>100950.732</v>
@@ -7634,7 +7633,7 @@
       <c r="AG100" s="1"/>
       <c r="AH100" s="1"/>
     </row>
-    <row r="101" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="101" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A101" s="4" t="s">
         <v>123</v>
       </c>
@@ -7666,12 +7665,12 @@
       <c r="J101" s="24"/>
       <c r="K101" s="24"/>
       <c r="L101" s="24"/>
-      <c r="M101" s="35"/>
-      <c r="N101" s="35"/>
-      <c r="O101" s="38"/>
-      <c r="P101" s="38"/>
-      <c r="Q101" s="38"/>
-      <c r="R101" s="38"/>
+      <c r="M101" s="28"/>
+      <c r="N101" s="28"/>
+      <c r="O101" s="31"/>
+      <c r="P101" s="31"/>
+      <c r="Q101" s="31"/>
+      <c r="R101" s="31"/>
       <c r="S101" s="13">
         <f t="shared" si="16"/>
         <v>107048.81700000002</v>
@@ -7692,7 +7691,7 @@
       <c r="AG101" s="1"/>
       <c r="AH101" s="1"/>
     </row>
-    <row r="102" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="102" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A102" s="4" t="s">
         <v>124</v>
       </c>
@@ -7724,12 +7723,12 @@
       <c r="J102" s="24"/>
       <c r="K102" s="24"/>
       <c r="L102" s="24"/>
-      <c r="M102" s="35"/>
-      <c r="N102" s="35"/>
-      <c r="O102" s="38"/>
-      <c r="P102" s="38"/>
-      <c r="Q102" s="38"/>
-      <c r="R102" s="38"/>
+      <c r="M102" s="28"/>
+      <c r="N102" s="28"/>
+      <c r="O102" s="31"/>
+      <c r="P102" s="31"/>
+      <c r="Q102" s="31"/>
+      <c r="R102" s="31"/>
       <c r="S102" s="13">
         <f t="shared" si="16"/>
         <v>101363.724</v>
@@ -7750,7 +7749,7 @@
       <c r="AG102" s="1"/>
       <c r="AH102" s="1"/>
     </row>
-    <row r="103" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="103" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A103" s="4" t="s">
         <v>125</v>
       </c>
@@ -7782,12 +7781,12 @@
       <c r="J103" s="24"/>
       <c r="K103" s="24"/>
       <c r="L103" s="24"/>
-      <c r="M103" s="35"/>
-      <c r="N103" s="35"/>
-      <c r="O103" s="38"/>
-      <c r="P103" s="38"/>
-      <c r="Q103" s="38"/>
-      <c r="R103" s="38"/>
+      <c r="M103" s="28"/>
+      <c r="N103" s="28"/>
+      <c r="O103" s="31"/>
+      <c r="P103" s="31"/>
+      <c r="Q103" s="31"/>
+      <c r="R103" s="31"/>
       <c r="S103" s="13">
         <f t="shared" si="16"/>
         <v>104846.19300000003</v>
@@ -7808,7 +7807,7 @@
       <c r="AG103" s="1"/>
       <c r="AH103" s="1"/>
     </row>
-    <row r="104" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="104" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A104" s="4" t="s">
         <v>126</v>
       </c>
@@ -7840,12 +7839,12 @@
       <c r="J104" s="24"/>
       <c r="K104" s="24"/>
       <c r="L104" s="24"/>
-      <c r="M104" s="35"/>
-      <c r="N104" s="35"/>
-      <c r="O104" s="38"/>
-      <c r="P104" s="38"/>
-      <c r="Q104" s="38"/>
-      <c r="R104" s="38"/>
+      <c r="M104" s="28"/>
+      <c r="N104" s="28"/>
+      <c r="O104" s="31"/>
+      <c r="P104" s="31"/>
+      <c r="Q104" s="31"/>
+      <c r="R104" s="31"/>
       <c r="S104" s="13">
         <f t="shared" si="16"/>
         <v>95895.882000000012</v>
@@ -7866,7 +7865,7 @@
       <c r="AG104" s="1"/>
       <c r="AH104" s="1"/>
     </row>
-    <row r="105" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="105" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A105" s="4" t="s">
         <v>127</v>
       </c>
@@ -7898,12 +7897,12 @@
       <c r="J105" s="24"/>
       <c r="K105" s="24"/>
       <c r="L105" s="24"/>
-      <c r="M105" s="35"/>
-      <c r="N105" s="35"/>
-      <c r="O105" s="38"/>
-      <c r="P105" s="38"/>
-      <c r="Q105" s="38"/>
-      <c r="R105" s="38"/>
+      <c r="M105" s="28"/>
+      <c r="N105" s="28"/>
+      <c r="O105" s="31"/>
+      <c r="P105" s="31"/>
+      <c r="Q105" s="31"/>
+      <c r="R105" s="31"/>
       <c r="S105" s="13">
         <f t="shared" si="16"/>
         <v>103486.76100000001</v>
@@ -7924,7 +7923,7 @@
       <c r="AG105" s="1"/>
       <c r="AH105" s="1"/>
     </row>
-    <row r="106" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="106" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A106" s="4" t="s">
         <v>128</v>
       </c>
@@ -7956,12 +7955,12 @@
       <c r="J106" s="24"/>
       <c r="K106" s="24"/>
       <c r="L106" s="24"/>
-      <c r="M106" s="35"/>
-      <c r="N106" s="35"/>
-      <c r="O106" s="38"/>
-      <c r="P106" s="38"/>
-      <c r="Q106" s="38"/>
-      <c r="R106" s="38"/>
+      <c r="M106" s="28"/>
+      <c r="N106" s="28"/>
+      <c r="O106" s="31"/>
+      <c r="P106" s="31"/>
+      <c r="Q106" s="31"/>
+      <c r="R106" s="31"/>
       <c r="S106" s="13">
         <f t="shared" si="16"/>
         <v>97020.854999999996</v>
@@ -7982,7 +7981,7 @@
       <c r="AG106" s="1"/>
       <c r="AH106" s="1"/>
     </row>
-    <row r="107" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="107" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A107" s="4" t="s">
         <v>129</v>
       </c>
@@ -8014,12 +8013,12 @@
       <c r="J107" s="24"/>
       <c r="K107" s="24"/>
       <c r="L107" s="24"/>
-      <c r="M107" s="35"/>
-      <c r="N107" s="35"/>
-      <c r="O107" s="38"/>
-      <c r="P107" s="38"/>
-      <c r="Q107" s="38"/>
-      <c r="R107" s="38"/>
+      <c r="M107" s="28"/>
+      <c r="N107" s="28"/>
+      <c r="O107" s="31"/>
+      <c r="P107" s="31"/>
+      <c r="Q107" s="31"/>
+      <c r="R107" s="31"/>
       <c r="S107" s="13">
         <f t="shared" si="16"/>
         <v>106932.663</v>
@@ -8040,7 +8039,7 @@
       <c r="AG107" s="1"/>
       <c r="AH107" s="1"/>
     </row>
-    <row r="108" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="108" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A108" s="4" t="s">
         <v>130</v>
       </c>
@@ -8072,12 +8071,12 @@
       <c r="J108" s="24"/>
       <c r="K108" s="24"/>
       <c r="L108" s="24"/>
-      <c r="M108" s="35"/>
-      <c r="N108" s="35"/>
-      <c r="O108" s="38"/>
-      <c r="P108" s="38"/>
-      <c r="Q108" s="38"/>
-      <c r="R108" s="38"/>
+      <c r="M108" s="28"/>
+      <c r="N108" s="28"/>
+      <c r="O108" s="31"/>
+      <c r="P108" s="31"/>
+      <c r="Q108" s="31"/>
+      <c r="R108" s="31"/>
       <c r="S108" s="13">
         <f t="shared" si="16"/>
         <v>95603.346000000005</v>
@@ -8098,7 +8097,7 @@
       <c r="AG108" s="1"/>
       <c r="AH108" s="1"/>
     </row>
-    <row r="109" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="109" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A109" s="4" t="s">
         <v>131</v>
       </c>
@@ -8130,12 +8129,12 @@
       <c r="J109" s="25"/>
       <c r="K109" s="25"/>
       <c r="L109" s="25"/>
-      <c r="M109" s="36"/>
-      <c r="N109" s="35"/>
-      <c r="O109" s="39"/>
-      <c r="P109" s="38"/>
-      <c r="Q109" s="38"/>
-      <c r="R109" s="38"/>
+      <c r="M109" s="29"/>
+      <c r="N109" s="28"/>
+      <c r="O109" s="32"/>
+      <c r="P109" s="31"/>
+      <c r="Q109" s="31"/>
+      <c r="R109" s="31"/>
       <c r="S109" s="13">
         <f t="shared" si="16"/>
         <v>114304.14000000001</v>
@@ -8156,7 +8155,7 @@
       <c r="AG109" s="1"/>
       <c r="AH109" s="1"/>
     </row>
-    <row r="110" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="110" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A110" s="4" t="s">
         <v>132</v>
       </c>
@@ -8192,18 +8191,18 @@
       <c r="L110" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="M110" s="34">
+      <c r="M110" s="27">
         <v>0.4</v>
       </c>
-      <c r="N110" s="34" t="s">
+      <c r="N110" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="O110" s="37">
+      <c r="O110" s="30">
         <v>11700</v>
       </c>
-      <c r="P110" s="40"/>
-      <c r="Q110" s="41"/>
-      <c r="R110" s="41"/>
+      <c r="P110" s="33"/>
+      <c r="Q110" s="34"/>
+      <c r="R110" s="34"/>
       <c r="S110" s="7">
         <f t="shared" ref="S110:S121" si="17">H110*$K$110*$M$110*$O$110</f>
         <v>5222.880000000001</v>
@@ -8224,7 +8223,7 @@
       <c r="AG110" s="1"/>
       <c r="AH110" s="1"/>
     </row>
-    <row r="111" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="111" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A111" s="4" t="s">
         <v>133</v>
       </c>
@@ -8256,12 +8255,12 @@
       <c r="J111" s="24"/>
       <c r="K111" s="24"/>
       <c r="L111" s="24"/>
-      <c r="M111" s="35"/>
-      <c r="N111" s="35"/>
-      <c r="O111" s="38"/>
-      <c r="P111" s="38"/>
-      <c r="Q111" s="38"/>
-      <c r="R111" s="38"/>
+      <c r="M111" s="28"/>
+      <c r="N111" s="28"/>
+      <c r="O111" s="31"/>
+      <c r="P111" s="31"/>
+      <c r="Q111" s="31"/>
+      <c r="R111" s="31"/>
       <c r="S111" s="7">
         <f t="shared" si="17"/>
         <v>5372.4059999999999</v>
@@ -8282,7 +8281,7 @@
       <c r="AG111" s="1"/>
       <c r="AH111" s="1"/>
     </row>
-    <row r="112" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="112" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A112" s="4" t="s">
         <v>134</v>
       </c>
@@ -8314,12 +8313,12 @@
       <c r="J112" s="24"/>
       <c r="K112" s="24"/>
       <c r="L112" s="24"/>
-      <c r="M112" s="35"/>
-      <c r="N112" s="35"/>
-      <c r="O112" s="38"/>
-      <c r="P112" s="38"/>
-      <c r="Q112" s="38"/>
-      <c r="R112" s="38"/>
+      <c r="M112" s="28"/>
+      <c r="N112" s="28"/>
+      <c r="O112" s="31"/>
+      <c r="P112" s="31"/>
+      <c r="Q112" s="31"/>
+      <c r="R112" s="31"/>
       <c r="S112" s="7">
         <f t="shared" si="17"/>
         <v>5517.72</v>
@@ -8340,7 +8339,7 @@
       <c r="AG112" s="1"/>
       <c r="AH112" s="1"/>
     </row>
-    <row r="113" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="113" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A113" s="4" t="s">
         <v>135</v>
       </c>
@@ -8372,12 +8371,12 @@
       <c r="J113" s="24"/>
       <c r="K113" s="24"/>
       <c r="L113" s="24"/>
-      <c r="M113" s="35"/>
-      <c r="N113" s="35"/>
-      <c r="O113" s="38"/>
-      <c r="P113" s="38"/>
-      <c r="Q113" s="38"/>
-      <c r="R113" s="38"/>
+      <c r="M113" s="28"/>
+      <c r="N113" s="28"/>
+      <c r="O113" s="31"/>
+      <c r="P113" s="31"/>
+      <c r="Q113" s="31"/>
+      <c r="R113" s="31"/>
       <c r="S113" s="7">
         <f t="shared" si="17"/>
         <v>4875.3900000000003</v>
@@ -8398,7 +8397,7 @@
       <c r="AG113" s="1"/>
       <c r="AH113" s="1"/>
     </row>
-    <row r="114" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="114" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A114" s="4" t="s">
         <v>136</v>
       </c>
@@ -8430,12 +8429,12 @@
       <c r="J114" s="24"/>
       <c r="K114" s="24"/>
       <c r="L114" s="24"/>
-      <c r="M114" s="35"/>
-      <c r="N114" s="35"/>
-      <c r="O114" s="38"/>
-      <c r="P114" s="38"/>
-      <c r="Q114" s="38"/>
-      <c r="R114" s="38"/>
+      <c r="M114" s="28"/>
+      <c r="N114" s="28"/>
+      <c r="O114" s="31"/>
+      <c r="P114" s="31"/>
+      <c r="Q114" s="31"/>
+      <c r="R114" s="31"/>
       <c r="S114" s="7">
         <f t="shared" si="17"/>
         <v>5248.152</v>
@@ -8456,7 +8455,7 @@
       <c r="AG114" s="1"/>
       <c r="AH114" s="1"/>
     </row>
-    <row r="115" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="115" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A115" s="4" t="s">
         <v>137</v>
       </c>
@@ -8488,12 +8487,12 @@
       <c r="J115" s="24"/>
       <c r="K115" s="24"/>
       <c r="L115" s="24"/>
-      <c r="M115" s="35"/>
-      <c r="N115" s="35"/>
-      <c r="O115" s="38"/>
-      <c r="P115" s="38"/>
-      <c r="Q115" s="38"/>
-      <c r="R115" s="38"/>
+      <c r="M115" s="28"/>
+      <c r="N115" s="28"/>
+      <c r="O115" s="31"/>
+      <c r="P115" s="31"/>
+      <c r="Q115" s="31"/>
+      <c r="R115" s="31"/>
       <c r="S115" s="7">
         <f t="shared" si="17"/>
         <v>4942.7820000000002</v>
@@ -8514,7 +8513,7 @@
       <c r="AG115" s="1"/>
       <c r="AH115" s="1"/>
     </row>
-    <row r="116" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="116" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A116" s="4" t="s">
         <v>138</v>
       </c>
@@ -8546,12 +8545,12 @@
       <c r="J116" s="24"/>
       <c r="K116" s="24"/>
       <c r="L116" s="24"/>
-      <c r="M116" s="35"/>
-      <c r="N116" s="35"/>
-      <c r="O116" s="38"/>
-      <c r="P116" s="38"/>
-      <c r="Q116" s="38"/>
-      <c r="R116" s="38"/>
+      <c r="M116" s="28"/>
+      <c r="N116" s="28"/>
+      <c r="O116" s="31"/>
+      <c r="P116" s="31"/>
+      <c r="Q116" s="31"/>
+      <c r="R116" s="31"/>
       <c r="S116" s="7">
         <f t="shared" si="17"/>
         <v>5092.3080000000009</v>
@@ -8572,7 +8571,7 @@
       <c r="AG116" s="1"/>
       <c r="AH116" s="1"/>
     </row>
-    <row r="117" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="117" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A117" s="4" t="s">
         <v>139</v>
       </c>
@@ -8604,12 +8603,12 @@
       <c r="J117" s="24"/>
       <c r="K117" s="24"/>
       <c r="L117" s="24"/>
-      <c r="M117" s="35"/>
-      <c r="N117" s="35"/>
-      <c r="O117" s="38"/>
-      <c r="P117" s="38"/>
-      <c r="Q117" s="38"/>
-      <c r="R117" s="38"/>
+      <c r="M117" s="28"/>
+      <c r="N117" s="28"/>
+      <c r="O117" s="31"/>
+      <c r="P117" s="31"/>
+      <c r="Q117" s="31"/>
+      <c r="R117" s="31"/>
       <c r="S117" s="7">
         <f t="shared" si="17"/>
         <v>5397.6780000000008</v>
@@ -8630,7 +8629,7 @@
       <c r="AG117" s="1"/>
       <c r="AH117" s="1"/>
     </row>
-    <row r="118" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="118" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A118" s="4" t="s">
         <v>140</v>
       </c>
@@ -8662,12 +8661,12 @@
       <c r="J118" s="24"/>
       <c r="K118" s="24"/>
       <c r="L118" s="24"/>
-      <c r="M118" s="35"/>
-      <c r="N118" s="35"/>
-      <c r="O118" s="38"/>
-      <c r="P118" s="38"/>
-      <c r="Q118" s="38"/>
-      <c r="R118" s="38"/>
+      <c r="M118" s="28"/>
+      <c r="N118" s="28"/>
+      <c r="O118" s="31"/>
+      <c r="P118" s="31"/>
+      <c r="Q118" s="31"/>
+      <c r="R118" s="31"/>
       <c r="S118" s="7">
         <f t="shared" si="17"/>
         <v>4814.3159999999998</v>
@@ -8688,7 +8687,7 @@
       <c r="AG118" s="1"/>
       <c r="AH118" s="1"/>
     </row>
-    <row r="119" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="119" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A119" s="4" t="s">
         <v>141</v>
       </c>
@@ -8720,12 +8719,12 @@
       <c r="J119" s="24"/>
       <c r="K119" s="24"/>
       <c r="L119" s="24"/>
-      <c r="M119" s="35"/>
-      <c r="N119" s="35"/>
-      <c r="O119" s="38"/>
-      <c r="P119" s="38"/>
-      <c r="Q119" s="38"/>
-      <c r="R119" s="38"/>
+      <c r="M119" s="28"/>
+      <c r="N119" s="28"/>
+      <c r="O119" s="31"/>
+      <c r="P119" s="31"/>
+      <c r="Q119" s="31"/>
+      <c r="R119" s="31"/>
       <c r="S119" s="7">
         <f t="shared" si="17"/>
         <v>5210.2440000000015</v>
@@ -8746,7 +8745,7 @@
       <c r="AG119" s="1"/>
       <c r="AH119" s="1"/>
     </row>
-    <row r="120" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="120" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A120" s="4" t="s">
         <v>142</v>
       </c>
@@ -8778,12 +8777,12 @@
       <c r="J120" s="24"/>
       <c r="K120" s="24"/>
       <c r="L120" s="24"/>
-      <c r="M120" s="35"/>
-      <c r="N120" s="35"/>
-      <c r="O120" s="38"/>
-      <c r="P120" s="38"/>
-      <c r="Q120" s="38"/>
-      <c r="R120" s="38"/>
+      <c r="M120" s="28"/>
+      <c r="N120" s="28"/>
+      <c r="O120" s="31"/>
+      <c r="P120" s="31"/>
+      <c r="Q120" s="31"/>
+      <c r="R120" s="31"/>
       <c r="S120" s="7">
         <f t="shared" si="17"/>
         <v>4906.9799999999996</v>
@@ -8804,7 +8803,7 @@
       <c r="AG120" s="1"/>
       <c r="AH120" s="1"/>
     </row>
-    <row r="121" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="121" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A121" s="4" t="s">
         <v>143</v>
       </c>
@@ -8836,12 +8835,12 @@
       <c r="J121" s="25"/>
       <c r="K121" s="25"/>
       <c r="L121" s="25"/>
-      <c r="M121" s="36"/>
-      <c r="N121" s="35"/>
-      <c r="O121" s="39"/>
-      <c r="P121" s="38"/>
-      <c r="Q121" s="38"/>
-      <c r="R121" s="38"/>
+      <c r="M121" s="29"/>
+      <c r="N121" s="28"/>
+      <c r="O121" s="32"/>
+      <c r="P121" s="31"/>
+      <c r="Q121" s="31"/>
+      <c r="R121" s="31"/>
       <c r="S121" s="7">
         <f t="shared" si="17"/>
         <v>4875.3900000000003</v>
@@ -8862,7 +8861,7 @@
       <c r="AG121" s="1"/>
       <c r="AH121" s="1"/>
     </row>
-    <row r="122" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="122" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A122" s="4" t="s">
         <v>144</v>
       </c>
@@ -8936,7 +8935,7 @@
       <c r="AG122" s="1"/>
       <c r="AH122" s="1"/>
     </row>
-    <row r="123" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="123" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A123" s="4" t="s">
         <v>145</v>
       </c>
@@ -8994,7 +8993,7 @@
       <c r="AG123" s="1"/>
       <c r="AH123" s="1"/>
     </row>
-    <row r="124" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="124" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A124" s="4" t="s">
         <v>146</v>
       </c>
@@ -9052,7 +9051,7 @@
       <c r="AG124" s="1"/>
       <c r="AH124" s="1"/>
     </row>
-    <row r="125" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="125" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A125" s="4" t="s">
         <v>147</v>
       </c>
@@ -9110,7 +9109,7 @@
       <c r="AG125" s="1"/>
       <c r="AH125" s="1"/>
     </row>
-    <row r="126" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="126" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A126" s="4" t="s">
         <v>148</v>
       </c>
@@ -9168,7 +9167,7 @@
       <c r="AG126" s="1"/>
       <c r="AH126" s="1"/>
     </row>
-    <row r="127" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="127" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A127" s="4" t="s">
         <v>149</v>
       </c>
@@ -9226,7 +9225,7 @@
       <c r="AG127" s="1"/>
       <c r="AH127" s="1"/>
     </row>
-    <row r="128" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="128" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A128" s="4" t="s">
         <v>150</v>
       </c>
@@ -9284,7 +9283,7 @@
       <c r="AG128" s="1"/>
       <c r="AH128" s="1"/>
     </row>
-    <row r="129" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="129" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A129" s="4" t="s">
         <v>151</v>
       </c>
@@ -9342,7 +9341,7 @@
       <c r="AG129" s="1"/>
       <c r="AH129" s="1"/>
     </row>
-    <row r="130" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="130" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A130" s="4" t="s">
         <v>152</v>
       </c>
@@ -9400,7 +9399,7 @@
       <c r="AG130" s="1"/>
       <c r="AH130" s="1"/>
     </row>
-    <row r="131" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="131" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A131" s="4" t="s">
         <v>153</v>
       </c>
@@ -9458,7 +9457,7 @@
       <c r="AG131" s="1"/>
       <c r="AH131" s="1"/>
     </row>
-    <row r="132" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="132" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A132" s="4" t="s">
         <v>154</v>
       </c>
@@ -9516,7 +9515,7 @@
       <c r="AG132" s="1"/>
       <c r="AH132" s="1"/>
     </row>
-    <row r="133" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="133" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A133" s="4" t="s">
         <v>155</v>
       </c>
@@ -9574,7 +9573,7 @@
       <c r="AG133" s="1"/>
       <c r="AH133" s="1"/>
     </row>
-    <row r="134" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="134" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A134" s="4" t="s">
         <v>156</v>
       </c>
@@ -9606,13 +9605,13 @@
       <c r="J134" s="26"/>
       <c r="K134" s="26"/>
       <c r="L134" s="26"/>
-      <c r="M134" s="31">
+      <c r="M134" s="36">
         <v>59510</v>
       </c>
-      <c r="N134" s="32">
+      <c r="N134" s="39">
         <v>1.8320000000000001</v>
       </c>
-      <c r="O134" s="33">
+      <c r="O134" s="40">
         <v>0.44</v>
       </c>
       <c r="P134" s="23">
@@ -9644,7 +9643,7 @@
       <c r="AG134" s="1"/>
       <c r="AH134" s="1"/>
     </row>
-    <row r="135" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="135" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A135" s="15" t="s">
         <v>157</v>
       </c>
@@ -9676,8 +9675,8 @@
       <c r="J135" s="24"/>
       <c r="K135" s="24"/>
       <c r="L135" s="24"/>
-      <c r="M135" s="29"/>
-      <c r="N135" s="29"/>
+      <c r="M135" s="37"/>
+      <c r="N135" s="37"/>
       <c r="O135" s="24"/>
       <c r="P135" s="24"/>
       <c r="Q135" s="24"/>
@@ -9702,7 +9701,7 @@
       <c r="AG135" s="1"/>
       <c r="AH135" s="1"/>
     </row>
-    <row r="136" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="136" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A136" s="15" t="s">
         <v>158</v>
       </c>
@@ -9734,8 +9733,8 @@
       <c r="J136" s="24"/>
       <c r="K136" s="24"/>
       <c r="L136" s="24"/>
-      <c r="M136" s="29"/>
-      <c r="N136" s="29"/>
+      <c r="M136" s="37"/>
+      <c r="N136" s="37"/>
       <c r="O136" s="24"/>
       <c r="P136" s="24"/>
       <c r="Q136" s="24"/>
@@ -9760,7 +9759,7 @@
       <c r="AG136" s="1"/>
       <c r="AH136" s="1"/>
     </row>
-    <row r="137" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="137" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A137" s="15" t="s">
         <v>159</v>
       </c>
@@ -9792,8 +9791,8 @@
       <c r="J137" s="24"/>
       <c r="K137" s="24"/>
       <c r="L137" s="24"/>
-      <c r="M137" s="29"/>
-      <c r="N137" s="29"/>
+      <c r="M137" s="37"/>
+      <c r="N137" s="37"/>
       <c r="O137" s="24"/>
       <c r="P137" s="24"/>
       <c r="Q137" s="24"/>
@@ -9818,7 +9817,7 @@
       <c r="AG137" s="1"/>
       <c r="AH137" s="1"/>
     </row>
-    <row r="138" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="138" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A138" s="15" t="s">
         <v>160</v>
       </c>
@@ -9850,8 +9849,8 @@
       <c r="J138" s="24"/>
       <c r="K138" s="24"/>
       <c r="L138" s="24"/>
-      <c r="M138" s="29"/>
-      <c r="N138" s="29"/>
+      <c r="M138" s="37"/>
+      <c r="N138" s="37"/>
       <c r="O138" s="24"/>
       <c r="P138" s="24"/>
       <c r="Q138" s="24"/>
@@ -9876,7 +9875,7 @@
       <c r="AG138" s="1"/>
       <c r="AH138" s="1"/>
     </row>
-    <row r="139" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="139" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A139" s="15" t="s">
         <v>161</v>
       </c>
@@ -9908,8 +9907,8 @@
       <c r="J139" s="24"/>
       <c r="K139" s="24"/>
       <c r="L139" s="24"/>
-      <c r="M139" s="29"/>
-      <c r="N139" s="29"/>
+      <c r="M139" s="37"/>
+      <c r="N139" s="37"/>
       <c r="O139" s="24"/>
       <c r="P139" s="24"/>
       <c r="Q139" s="24"/>
@@ -9934,7 +9933,7 @@
       <c r="AG139" s="1"/>
       <c r="AH139" s="1"/>
     </row>
-    <row r="140" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="140" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A140" s="15" t="s">
         <v>162</v>
       </c>
@@ -9966,8 +9965,8 @@
       <c r="J140" s="24"/>
       <c r="K140" s="24"/>
       <c r="L140" s="24"/>
-      <c r="M140" s="29"/>
-      <c r="N140" s="29"/>
+      <c r="M140" s="37"/>
+      <c r="N140" s="37"/>
       <c r="O140" s="24"/>
       <c r="P140" s="24"/>
       <c r="Q140" s="24"/>
@@ -9992,7 +9991,7 @@
       <c r="AG140" s="1"/>
       <c r="AH140" s="1"/>
     </row>
-    <row r="141" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="141" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A141" s="15" t="s">
         <v>163</v>
       </c>
@@ -10024,8 +10023,8 @@
       <c r="J141" s="24"/>
       <c r="K141" s="24"/>
       <c r="L141" s="24"/>
-      <c r="M141" s="29"/>
-      <c r="N141" s="29"/>
+      <c r="M141" s="37"/>
+      <c r="N141" s="37"/>
       <c r="O141" s="24"/>
       <c r="P141" s="24"/>
       <c r="Q141" s="24"/>
@@ -10050,7 +10049,7 @@
       <c r="AG141" s="1"/>
       <c r="AH141" s="1"/>
     </row>
-    <row r="142" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="142" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A142" s="15" t="s">
         <v>164</v>
       </c>
@@ -10082,8 +10081,8 @@
       <c r="J142" s="24"/>
       <c r="K142" s="24"/>
       <c r="L142" s="24"/>
-      <c r="M142" s="29"/>
-      <c r="N142" s="29"/>
+      <c r="M142" s="37"/>
+      <c r="N142" s="37"/>
       <c r="O142" s="24"/>
       <c r="P142" s="24"/>
       <c r="Q142" s="24"/>
@@ -10108,7 +10107,7 @@
       <c r="AG142" s="1"/>
       <c r="AH142" s="1"/>
     </row>
-    <row r="143" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="143" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A143" s="15" t="s">
         <v>165</v>
       </c>
@@ -10140,8 +10139,8 @@
       <c r="J143" s="24"/>
       <c r="K143" s="24"/>
       <c r="L143" s="24"/>
-      <c r="M143" s="29"/>
-      <c r="N143" s="29"/>
+      <c r="M143" s="37"/>
+      <c r="N143" s="37"/>
       <c r="O143" s="24"/>
       <c r="P143" s="24"/>
       <c r="Q143" s="24"/>
@@ -10166,7 +10165,7 @@
       <c r="AG143" s="1"/>
       <c r="AH143" s="1"/>
     </row>
-    <row r="144" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="144" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A144" s="15" t="s">
         <v>166</v>
       </c>
@@ -10198,8 +10197,8 @@
       <c r="J144" s="24"/>
       <c r="K144" s="24"/>
       <c r="L144" s="24"/>
-      <c r="M144" s="29"/>
-      <c r="N144" s="29"/>
+      <c r="M144" s="37"/>
+      <c r="N144" s="37"/>
       <c r="O144" s="24"/>
       <c r="P144" s="24"/>
       <c r="Q144" s="24"/>
@@ -10224,7 +10223,7 @@
       <c r="AG144" s="1"/>
       <c r="AH144" s="1"/>
     </row>
-    <row r="145" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="145" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A145" s="15" t="s">
         <v>167</v>
       </c>
@@ -10256,8 +10255,8 @@
       <c r="J145" s="25"/>
       <c r="K145" s="25"/>
       <c r="L145" s="25"/>
-      <c r="M145" s="30"/>
-      <c r="N145" s="30"/>
+      <c r="M145" s="38"/>
+      <c r="N145" s="38"/>
       <c r="O145" s="25"/>
       <c r="P145" s="25"/>
       <c r="Q145" s="25"/>
@@ -10311,7 +10310,7 @@
       <c r="I146" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J146" s="28">
+      <c r="J146" s="41">
         <v>43.1</v>
       </c>
       <c r="K146" s="26">
@@ -10320,7 +10319,7 @@
       <c r="L146" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="M146" s="27">
+      <c r="M146" s="35">
         <v>56100</v>
       </c>
       <c r="N146" s="26">
@@ -10387,7 +10386,7 @@
       <c r="I147" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J147" s="29"/>
+      <c r="J147" s="37"/>
       <c r="K147" s="24"/>
       <c r="L147" s="24"/>
       <c r="M147" s="24"/>
@@ -10445,7 +10444,7 @@
       <c r="I148" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J148" s="29"/>
+      <c r="J148" s="37"/>
       <c r="K148" s="24"/>
       <c r="L148" s="24"/>
       <c r="M148" s="24"/>
@@ -10503,7 +10502,7 @@
       <c r="I149" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J149" s="29"/>
+      <c r="J149" s="37"/>
       <c r="K149" s="24"/>
       <c r="L149" s="24"/>
       <c r="M149" s="24"/>
@@ -10561,7 +10560,7 @@
       <c r="I150" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J150" s="29"/>
+      <c r="J150" s="37"/>
       <c r="K150" s="24"/>
       <c r="L150" s="24"/>
       <c r="M150" s="24"/>
@@ -10619,7 +10618,7 @@
       <c r="I151" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J151" s="29"/>
+      <c r="J151" s="37"/>
       <c r="K151" s="24"/>
       <c r="L151" s="24"/>
       <c r="M151" s="24"/>
@@ -10677,7 +10676,7 @@
       <c r="I152" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J152" s="29"/>
+      <c r="J152" s="37"/>
       <c r="K152" s="24"/>
       <c r="L152" s="24"/>
       <c r="M152" s="24"/>
@@ -10735,7 +10734,7 @@
       <c r="I153" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J153" s="29"/>
+      <c r="J153" s="37"/>
       <c r="K153" s="24"/>
       <c r="L153" s="24"/>
       <c r="M153" s="24"/>
@@ -10793,7 +10792,7 @@
       <c r="I154" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J154" s="29"/>
+      <c r="J154" s="37"/>
       <c r="K154" s="24"/>
       <c r="L154" s="24"/>
       <c r="M154" s="24"/>
@@ -10851,7 +10850,7 @@
       <c r="I155" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J155" s="29"/>
+      <c r="J155" s="37"/>
       <c r="K155" s="24"/>
       <c r="L155" s="24"/>
       <c r="M155" s="24"/>
@@ -10909,7 +10908,7 @@
       <c r="I156" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J156" s="29"/>
+      <c r="J156" s="37"/>
       <c r="K156" s="24"/>
       <c r="L156" s="24"/>
       <c r="M156" s="24"/>
@@ -10967,7 +10966,7 @@
       <c r="I157" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J157" s="30"/>
+      <c r="J157" s="38"/>
       <c r="K157" s="25"/>
       <c r="L157" s="25"/>
       <c r="M157" s="25"/>
@@ -10996,7 +10995,7 @@
       <c r="AG157" s="1"/>
       <c r="AH157" s="1"/>
     </row>
-    <row r="158" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="158" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A158" s="4" t="s">
         <v>180</v>
       </c>
@@ -11034,13 +11033,13 @@
       <c r="L158" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="M158" s="27">
+      <c r="M158" s="35">
         <v>69300</v>
       </c>
-      <c r="N158" s="27">
+      <c r="N158" s="35">
         <v>25</v>
       </c>
-      <c r="O158" s="27">
+      <c r="O158" s="35">
         <v>8</v>
       </c>
       <c r="P158" s="23">
@@ -11072,7 +11071,7 @@
       <c r="AG158" s="1"/>
       <c r="AH158" s="1"/>
     </row>
-    <row r="159" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="159" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A159" s="4" t="s">
         <v>181</v>
       </c>
@@ -11130,7 +11129,7 @@
       <c r="AG159" s="1"/>
       <c r="AH159" s="1"/>
     </row>
-    <row r="160" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="160" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A160" s="4" t="s">
         <v>182</v>
       </c>
@@ -11188,7 +11187,7 @@
       <c r="AG160" s="1"/>
       <c r="AH160" s="1"/>
     </row>
-    <row r="161" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="161" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A161" s="4" t="s">
         <v>183</v>
       </c>
@@ -11246,7 +11245,7 @@
       <c r="AG161" s="1"/>
       <c r="AH161" s="1"/>
     </row>
-    <row r="162" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="162" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A162" s="4" t="s">
         <v>184</v>
       </c>
@@ -11304,7 +11303,7 @@
       <c r="AG162" s="1"/>
       <c r="AH162" s="1"/>
     </row>
-    <row r="163" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="163" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A163" s="4" t="s">
         <v>185</v>
       </c>
@@ -11362,7 +11361,7 @@
       <c r="AG163" s="1"/>
       <c r="AH163" s="1"/>
     </row>
-    <row r="164" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="164" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A164" s="4" t="s">
         <v>186</v>
       </c>
@@ -11420,7 +11419,7 @@
       <c r="AG164" s="1"/>
       <c r="AH164" s="1"/>
     </row>
-    <row r="165" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="165" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A165" s="4" t="s">
         <v>187</v>
       </c>
@@ -11478,7 +11477,7 @@
       <c r="AG165" s="1"/>
       <c r="AH165" s="1"/>
     </row>
-    <row r="166" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="166" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A166" s="4" t="s">
         <v>188</v>
       </c>
@@ -11536,7 +11535,7 @@
       <c r="AG166" s="1"/>
       <c r="AH166" s="1"/>
     </row>
-    <row r="167" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="167" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A167" s="4" t="s">
         <v>189</v>
       </c>
@@ -11594,7 +11593,7 @@
       <c r="AG167" s="1"/>
       <c r="AH167" s="1"/>
     </row>
-    <row r="168" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="168" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A168" s="4" t="s">
         <v>190</v>
       </c>
@@ -11652,7 +11651,7 @@
       <c r="AG168" s="1"/>
       <c r="AH168" s="1"/>
     </row>
-    <row r="169" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="169" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A169" s="4" t="s">
         <v>191</v>
       </c>
@@ -11710,7 +11709,7 @@
       <c r="AG169" s="1"/>
       <c r="AH169" s="1"/>
     </row>
-    <row r="170" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="170" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A170" s="4" t="s">
         <v>192</v>
       </c>
@@ -11746,18 +11745,18 @@
       <c r="L170" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="M170" s="34">
+      <c r="M170" s="27">
         <v>0.2</v>
       </c>
-      <c r="N170" s="34" t="s">
+      <c r="N170" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="O170" s="37">
+      <c r="O170" s="30">
         <v>23900</v>
       </c>
-      <c r="P170" s="40"/>
-      <c r="Q170" s="41"/>
-      <c r="R170" s="41"/>
+      <c r="P170" s="33"/>
+      <c r="Q170" s="34"/>
+      <c r="R170" s="34"/>
       <c r="S170" s="13">
         <f t="shared" ref="S170:S181" si="27">H170*$K$170*$M$170*$O$170</f>
         <v>0</v>
@@ -11778,7 +11777,7 @@
       <c r="AG170" s="1"/>
       <c r="AH170" s="1"/>
     </row>
-    <row r="171" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="171" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A171" s="4" t="s">
         <v>193</v>
       </c>
@@ -11810,12 +11809,12 @@
       <c r="J171" s="24"/>
       <c r="K171" s="24"/>
       <c r="L171" s="24"/>
-      <c r="M171" s="35"/>
-      <c r="N171" s="35"/>
-      <c r="O171" s="38"/>
-      <c r="P171" s="38"/>
-      <c r="Q171" s="38"/>
-      <c r="R171" s="38"/>
+      <c r="M171" s="28"/>
+      <c r="N171" s="28"/>
+      <c r="O171" s="31"/>
+      <c r="P171" s="31"/>
+      <c r="Q171" s="31"/>
+      <c r="R171" s="31"/>
       <c r="S171" s="13">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -11836,7 +11835,7 @@
       <c r="AG171" s="1"/>
       <c r="AH171" s="1"/>
     </row>
-    <row r="172" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="172" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A172" s="4" t="s">
         <v>194</v>
       </c>
@@ -11868,12 +11867,12 @@
       <c r="J172" s="24"/>
       <c r="K172" s="24"/>
       <c r="L172" s="24"/>
-      <c r="M172" s="35"/>
-      <c r="N172" s="35"/>
-      <c r="O172" s="38"/>
-      <c r="P172" s="38"/>
-      <c r="Q172" s="38"/>
-      <c r="R172" s="38"/>
+      <c r="M172" s="28"/>
+      <c r="N172" s="28"/>
+      <c r="O172" s="31"/>
+      <c r="P172" s="31"/>
+      <c r="Q172" s="31"/>
+      <c r="R172" s="31"/>
       <c r="S172" s="13">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -11894,7 +11893,7 @@
       <c r="AG172" s="1"/>
       <c r="AH172" s="1"/>
     </row>
-    <row r="173" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="173" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A173" s="4" t="s">
         <v>195</v>
       </c>
@@ -11926,12 +11925,12 @@
       <c r="J173" s="24"/>
       <c r="K173" s="24"/>
       <c r="L173" s="24"/>
-      <c r="M173" s="35"/>
-      <c r="N173" s="35"/>
-      <c r="O173" s="38"/>
-      <c r="P173" s="38"/>
-      <c r="Q173" s="38"/>
-      <c r="R173" s="38"/>
+      <c r="M173" s="28"/>
+      <c r="N173" s="28"/>
+      <c r="O173" s="31"/>
+      <c r="P173" s="31"/>
+      <c r="Q173" s="31"/>
+      <c r="R173" s="31"/>
       <c r="S173" s="13">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -11952,7 +11951,7 @@
       <c r="AG173" s="1"/>
       <c r="AH173" s="1"/>
     </row>
-    <row r="174" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="174" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A174" s="4" t="s">
         <v>196</v>
       </c>
@@ -11984,12 +11983,12 @@
       <c r="J174" s="24"/>
       <c r="K174" s="24"/>
       <c r="L174" s="24"/>
-      <c r="M174" s="35"/>
-      <c r="N174" s="35"/>
-      <c r="O174" s="38"/>
-      <c r="P174" s="38"/>
-      <c r="Q174" s="38"/>
-      <c r="R174" s="38"/>
+      <c r="M174" s="28"/>
+      <c r="N174" s="28"/>
+      <c r="O174" s="31"/>
+      <c r="P174" s="31"/>
+      <c r="Q174" s="31"/>
+      <c r="R174" s="31"/>
       <c r="S174" s="13">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -12010,7 +12009,7 @@
       <c r="AG174" s="1"/>
       <c r="AH174" s="1"/>
     </row>
-    <row r="175" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="175" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A175" s="4" t="s">
         <v>197</v>
       </c>
@@ -12042,12 +12041,12 @@
       <c r="J175" s="24"/>
       <c r="K175" s="24"/>
       <c r="L175" s="24"/>
-      <c r="M175" s="35"/>
-      <c r="N175" s="35"/>
-      <c r="O175" s="38"/>
-      <c r="P175" s="38"/>
-      <c r="Q175" s="38"/>
-      <c r="R175" s="38"/>
+      <c r="M175" s="28"/>
+      <c r="N175" s="28"/>
+      <c r="O175" s="31"/>
+      <c r="P175" s="31"/>
+      <c r="Q175" s="31"/>
+      <c r="R175" s="31"/>
       <c r="S175" s="13">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -12068,7 +12067,7 @@
       <c r="AG175" s="1"/>
       <c r="AH175" s="1"/>
     </row>
-    <row r="176" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="176" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A176" s="4" t="s">
         <v>198</v>
       </c>
@@ -12100,12 +12099,12 @@
       <c r="J176" s="24"/>
       <c r="K176" s="24"/>
       <c r="L176" s="24"/>
-      <c r="M176" s="35"/>
-      <c r="N176" s="35"/>
-      <c r="O176" s="38"/>
-      <c r="P176" s="38"/>
-      <c r="Q176" s="38"/>
-      <c r="R176" s="38"/>
+      <c r="M176" s="28"/>
+      <c r="N176" s="28"/>
+      <c r="O176" s="31"/>
+      <c r="P176" s="31"/>
+      <c r="Q176" s="31"/>
+      <c r="R176" s="31"/>
       <c r="S176" s="13">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -12126,7 +12125,7 @@
       <c r="AG176" s="1"/>
       <c r="AH176" s="1"/>
     </row>
-    <row r="177" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="177" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A177" s="4" t="s">
         <v>199</v>
       </c>
@@ -12158,12 +12157,12 @@
       <c r="J177" s="24"/>
       <c r="K177" s="24"/>
       <c r="L177" s="24"/>
-      <c r="M177" s="35"/>
-      <c r="N177" s="35"/>
-      <c r="O177" s="38"/>
-      <c r="P177" s="38"/>
-      <c r="Q177" s="38"/>
-      <c r="R177" s="38"/>
+      <c r="M177" s="28"/>
+      <c r="N177" s="28"/>
+      <c r="O177" s="31"/>
+      <c r="P177" s="31"/>
+      <c r="Q177" s="31"/>
+      <c r="R177" s="31"/>
       <c r="S177" s="13">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -12184,7 +12183,7 @@
       <c r="AG177" s="1"/>
       <c r="AH177" s="1"/>
     </row>
-    <row r="178" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="178" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A178" s="4" t="s">
         <v>200</v>
       </c>
@@ -12216,12 +12215,12 @@
       <c r="J178" s="24"/>
       <c r="K178" s="24"/>
       <c r="L178" s="24"/>
-      <c r="M178" s="35"/>
-      <c r="N178" s="35"/>
-      <c r="O178" s="38"/>
-      <c r="P178" s="38"/>
-      <c r="Q178" s="38"/>
-      <c r="R178" s="38"/>
+      <c r="M178" s="28"/>
+      <c r="N178" s="28"/>
+      <c r="O178" s="31"/>
+      <c r="P178" s="31"/>
+      <c r="Q178" s="31"/>
+      <c r="R178" s="31"/>
       <c r="S178" s="13">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -12242,7 +12241,7 @@
       <c r="AG178" s="1"/>
       <c r="AH178" s="1"/>
     </row>
-    <row r="179" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="179" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A179" s="4" t="s">
         <v>201</v>
       </c>
@@ -12274,12 +12273,12 @@
       <c r="J179" s="24"/>
       <c r="K179" s="24"/>
       <c r="L179" s="24"/>
-      <c r="M179" s="35"/>
-      <c r="N179" s="35"/>
-      <c r="O179" s="38"/>
-      <c r="P179" s="38"/>
-      <c r="Q179" s="38"/>
-      <c r="R179" s="38"/>
+      <c r="M179" s="28"/>
+      <c r="N179" s="28"/>
+      <c r="O179" s="31"/>
+      <c r="P179" s="31"/>
+      <c r="Q179" s="31"/>
+      <c r="R179" s="31"/>
       <c r="S179" s="13">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -12300,7 +12299,7 @@
       <c r="AG179" s="1"/>
       <c r="AH179" s="1"/>
     </row>
-    <row r="180" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="180" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A180" s="4" t="s">
         <v>202</v>
       </c>
@@ -12332,12 +12331,12 @@
       <c r="J180" s="24"/>
       <c r="K180" s="24"/>
       <c r="L180" s="24"/>
-      <c r="M180" s="35"/>
-      <c r="N180" s="35"/>
-      <c r="O180" s="38"/>
-      <c r="P180" s="38"/>
-      <c r="Q180" s="38"/>
-      <c r="R180" s="38"/>
+      <c r="M180" s="28"/>
+      <c r="N180" s="28"/>
+      <c r="O180" s="31"/>
+      <c r="P180" s="31"/>
+      <c r="Q180" s="31"/>
+      <c r="R180" s="31"/>
       <c r="S180" s="13">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -12358,7 +12357,7 @@
       <c r="AG180" s="1"/>
       <c r="AH180" s="1"/>
     </row>
-    <row r="181" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="181" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A181" s="4" t="s">
         <v>203</v>
       </c>
@@ -12390,12 +12389,12 @@
       <c r="J181" s="25"/>
       <c r="K181" s="25"/>
       <c r="L181" s="25"/>
-      <c r="M181" s="36"/>
-      <c r="N181" s="35"/>
-      <c r="O181" s="39"/>
-      <c r="P181" s="38"/>
-      <c r="Q181" s="38"/>
-      <c r="R181" s="38"/>
+      <c r="M181" s="29"/>
+      <c r="N181" s="28"/>
+      <c r="O181" s="32"/>
+      <c r="P181" s="31"/>
+      <c r="Q181" s="31"/>
+      <c r="R181" s="31"/>
       <c r="S181" s="13">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -12416,7 +12415,7 @@
       <c r="AG181" s="1"/>
       <c r="AH181" s="1"/>
     </row>
-    <row r="182" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="182" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A182" s="4" t="s">
         <v>204</v>
       </c>
@@ -12452,18 +12451,18 @@
       <c r="L182" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="M182" s="34">
+      <c r="M182" s="27">
         <v>0.4</v>
       </c>
-      <c r="N182" s="34" t="s">
+      <c r="N182" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="O182" s="37">
+      <c r="O182" s="30">
         <v>11700</v>
       </c>
-      <c r="P182" s="40"/>
-      <c r="Q182" s="41"/>
-      <c r="R182" s="41"/>
+      <c r="P182" s="33"/>
+      <c r="Q182" s="34"/>
+      <c r="R182" s="34"/>
       <c r="S182" s="7">
         <f t="shared" ref="S182:S193" si="28">H182*$K$182*$M$182*$O$182</f>
         <v>0</v>
@@ -12484,7 +12483,7 @@
       <c r="AG182" s="1"/>
       <c r="AH182" s="1"/>
     </row>
-    <row r="183" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="183" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A183" s="4" t="s">
         <v>205</v>
       </c>
@@ -12516,12 +12515,12 @@
       <c r="J183" s="24"/>
       <c r="K183" s="24"/>
       <c r="L183" s="24"/>
-      <c r="M183" s="35"/>
-      <c r="N183" s="35"/>
-      <c r="O183" s="38"/>
-      <c r="P183" s="38"/>
-      <c r="Q183" s="38"/>
-      <c r="R183" s="38"/>
+      <c r="M183" s="28"/>
+      <c r="N183" s="28"/>
+      <c r="O183" s="31"/>
+      <c r="P183" s="31"/>
+      <c r="Q183" s="31"/>
+      <c r="R183" s="31"/>
       <c r="S183" s="7">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -12542,7 +12541,7 @@
       <c r="AG183" s="1"/>
       <c r="AH183" s="1"/>
     </row>
-    <row r="184" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="184" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A184" s="4" t="s">
         <v>206</v>
       </c>
@@ -12574,12 +12573,12 @@
       <c r="J184" s="24"/>
       <c r="K184" s="24"/>
       <c r="L184" s="24"/>
-      <c r="M184" s="35"/>
-      <c r="N184" s="35"/>
-      <c r="O184" s="38"/>
-      <c r="P184" s="38"/>
-      <c r="Q184" s="38"/>
-      <c r="R184" s="38"/>
+      <c r="M184" s="28"/>
+      <c r="N184" s="28"/>
+      <c r="O184" s="31"/>
+      <c r="P184" s="31"/>
+      <c r="Q184" s="31"/>
+      <c r="R184" s="31"/>
       <c r="S184" s="7">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -12600,7 +12599,7 @@
       <c r="AG184" s="1"/>
       <c r="AH184" s="1"/>
     </row>
-    <row r="185" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="185" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A185" s="4" t="s">
         <v>207</v>
       </c>
@@ -12632,12 +12631,12 @@
       <c r="J185" s="24"/>
       <c r="K185" s="24"/>
       <c r="L185" s="24"/>
-      <c r="M185" s="35"/>
-      <c r="N185" s="35"/>
-      <c r="O185" s="38"/>
-      <c r="P185" s="38"/>
-      <c r="Q185" s="38"/>
-      <c r="R185" s="38"/>
+      <c r="M185" s="28"/>
+      <c r="N185" s="28"/>
+      <c r="O185" s="31"/>
+      <c r="P185" s="31"/>
+      <c r="Q185" s="31"/>
+      <c r="R185" s="31"/>
       <c r="S185" s="7">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -12658,7 +12657,7 @@
       <c r="AG185" s="1"/>
       <c r="AH185" s="1"/>
     </row>
-    <row r="186" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="186" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A186" s="4" t="s">
         <v>208</v>
       </c>
@@ -12690,12 +12689,12 @@
       <c r="J186" s="24"/>
       <c r="K186" s="24"/>
       <c r="L186" s="24"/>
-      <c r="M186" s="35"/>
-      <c r="N186" s="35"/>
-      <c r="O186" s="38"/>
-      <c r="P186" s="38"/>
-      <c r="Q186" s="38"/>
-      <c r="R186" s="38"/>
+      <c r="M186" s="28"/>
+      <c r="N186" s="28"/>
+      <c r="O186" s="31"/>
+      <c r="P186" s="31"/>
+      <c r="Q186" s="31"/>
+      <c r="R186" s="31"/>
       <c r="S186" s="7">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -12716,7 +12715,7 @@
       <c r="AG186" s="1"/>
       <c r="AH186" s="1"/>
     </row>
-    <row r="187" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="187" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A187" s="4" t="s">
         <v>209</v>
       </c>
@@ -12748,12 +12747,12 @@
       <c r="J187" s="24"/>
       <c r="K187" s="24"/>
       <c r="L187" s="24"/>
-      <c r="M187" s="35"/>
-      <c r="N187" s="35"/>
-      <c r="O187" s="38"/>
-      <c r="P187" s="38"/>
-      <c r="Q187" s="38"/>
-      <c r="R187" s="38"/>
+      <c r="M187" s="28"/>
+      <c r="N187" s="28"/>
+      <c r="O187" s="31"/>
+      <c r="P187" s="31"/>
+      <c r="Q187" s="31"/>
+      <c r="R187" s="31"/>
       <c r="S187" s="7">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -12774,7 +12773,7 @@
       <c r="AG187" s="1"/>
       <c r="AH187" s="1"/>
     </row>
-    <row r="188" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="188" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A188" s="4" t="s">
         <v>210</v>
       </c>
@@ -12806,12 +12805,12 @@
       <c r="J188" s="24"/>
       <c r="K188" s="24"/>
       <c r="L188" s="24"/>
-      <c r="M188" s="35"/>
-      <c r="N188" s="35"/>
-      <c r="O188" s="38"/>
-      <c r="P188" s="38"/>
-      <c r="Q188" s="38"/>
-      <c r="R188" s="38"/>
+      <c r="M188" s="28"/>
+      <c r="N188" s="28"/>
+      <c r="O188" s="31"/>
+      <c r="P188" s="31"/>
+      <c r="Q188" s="31"/>
+      <c r="R188" s="31"/>
       <c r="S188" s="7">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -12832,7 +12831,7 @@
       <c r="AG188" s="1"/>
       <c r="AH188" s="1"/>
     </row>
-    <row r="189" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="189" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A189" s="4" t="s">
         <v>211</v>
       </c>
@@ -12864,12 +12863,12 @@
       <c r="J189" s="24"/>
       <c r="K189" s="24"/>
       <c r="L189" s="24"/>
-      <c r="M189" s="35"/>
-      <c r="N189" s="35"/>
-      <c r="O189" s="38"/>
-      <c r="P189" s="38"/>
-      <c r="Q189" s="38"/>
-      <c r="R189" s="38"/>
+      <c r="M189" s="28"/>
+      <c r="N189" s="28"/>
+      <c r="O189" s="31"/>
+      <c r="P189" s="31"/>
+      <c r="Q189" s="31"/>
+      <c r="R189" s="31"/>
       <c r="S189" s="7">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -12890,7 +12889,7 @@
       <c r="AG189" s="1"/>
       <c r="AH189" s="1"/>
     </row>
-    <row r="190" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="190" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A190" s="4" t="s">
         <v>212</v>
       </c>
@@ -12922,12 +12921,12 @@
       <c r="J190" s="24"/>
       <c r="K190" s="24"/>
       <c r="L190" s="24"/>
-      <c r="M190" s="35"/>
-      <c r="N190" s="35"/>
-      <c r="O190" s="38"/>
-      <c r="P190" s="38"/>
-      <c r="Q190" s="38"/>
-      <c r="R190" s="38"/>
+      <c r="M190" s="28"/>
+      <c r="N190" s="28"/>
+      <c r="O190" s="31"/>
+      <c r="P190" s="31"/>
+      <c r="Q190" s="31"/>
+      <c r="R190" s="31"/>
       <c r="S190" s="7">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -12948,7 +12947,7 @@
       <c r="AG190" s="1"/>
       <c r="AH190" s="1"/>
     </row>
-    <row r="191" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="191" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A191" s="4" t="s">
         <v>213</v>
       </c>
@@ -12980,12 +12979,12 @@
       <c r="J191" s="24"/>
       <c r="K191" s="24"/>
       <c r="L191" s="24"/>
-      <c r="M191" s="35"/>
-      <c r="N191" s="35"/>
-      <c r="O191" s="38"/>
-      <c r="P191" s="38"/>
-      <c r="Q191" s="38"/>
-      <c r="R191" s="38"/>
+      <c r="M191" s="28"/>
+      <c r="N191" s="28"/>
+      <c r="O191" s="31"/>
+      <c r="P191" s="31"/>
+      <c r="Q191" s="31"/>
+      <c r="R191" s="31"/>
       <c r="S191" s="7">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -13006,7 +13005,7 @@
       <c r="AG191" s="1"/>
       <c r="AH191" s="1"/>
     </row>
-    <row r="192" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="192" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A192" s="4" t="s">
         <v>214</v>
       </c>
@@ -13038,12 +13037,12 @@
       <c r="J192" s="24"/>
       <c r="K192" s="24"/>
       <c r="L192" s="24"/>
-      <c r="M192" s="35"/>
-      <c r="N192" s="35"/>
-      <c r="O192" s="38"/>
-      <c r="P192" s="38"/>
-      <c r="Q192" s="38"/>
-      <c r="R192" s="38"/>
+      <c r="M192" s="28"/>
+      <c r="N192" s="28"/>
+      <c r="O192" s="31"/>
+      <c r="P192" s="31"/>
+      <c r="Q192" s="31"/>
+      <c r="R192" s="31"/>
       <c r="S192" s="7">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -13064,7 +13063,7 @@
       <c r="AG192" s="1"/>
       <c r="AH192" s="1"/>
     </row>
-    <row r="193" spans="1:34" ht="15.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="193" spans="1:34" ht="15.75" customHeight="1" thickBot="1">
       <c r="A193" s="4" t="s">
         <v>215</v>
       </c>
@@ -13096,12 +13095,12 @@
       <c r="J193" s="25"/>
       <c r="K193" s="25"/>
       <c r="L193" s="25"/>
-      <c r="M193" s="36"/>
-      <c r="N193" s="35"/>
-      <c r="O193" s="39"/>
-      <c r="P193" s="38"/>
-      <c r="Q193" s="38"/>
-      <c r="R193" s="38"/>
+      <c r="M193" s="29"/>
+      <c r="N193" s="28"/>
+      <c r="O193" s="32"/>
+      <c r="P193" s="31"/>
+      <c r="Q193" s="31"/>
+      <c r="R193" s="31"/>
       <c r="S193" s="7">
         <f t="shared" si="28"/>
         <v>0</v>
@@ -13122,7 +13121,7 @@
       <c r="AG193" s="1"/>
       <c r="AH193" s="1"/>
     </row>
-    <row r="194" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="194" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A194" s="4" t="s">
         <v>216</v>
       </c>
@@ -13196,7 +13195,7 @@
       <c r="AG194" s="1"/>
       <c r="AH194" s="1"/>
     </row>
-    <row r="195" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="195" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A195" s="4" t="s">
         <v>217</v>
       </c>
@@ -13254,7 +13253,7 @@
       <c r="AG195" s="1"/>
       <c r="AH195" s="1"/>
     </row>
-    <row r="196" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="196" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A196" s="4" t="s">
         <v>218</v>
       </c>
@@ -13312,7 +13311,7 @@
       <c r="AG196" s="1"/>
       <c r="AH196" s="1"/>
     </row>
-    <row r="197" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="197" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A197" s="4" t="s">
         <v>219</v>
       </c>
@@ -13370,7 +13369,7 @@
       <c r="AG197" s="1"/>
       <c r="AH197" s="1"/>
     </row>
-    <row r="198" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="198" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A198" s="4" t="s">
         <v>220</v>
       </c>
@@ -13428,7 +13427,7 @@
       <c r="AG198" s="1"/>
       <c r="AH198" s="1"/>
     </row>
-    <row r="199" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="199" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A199" s="4" t="s">
         <v>221</v>
       </c>
@@ -13486,7 +13485,7 @@
       <c r="AG199" s="1"/>
       <c r="AH199" s="1"/>
     </row>
-    <row r="200" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="200" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A200" s="4" t="s">
         <v>222</v>
       </c>
@@ -13544,7 +13543,7 @@
       <c r="AG200" s="1"/>
       <c r="AH200" s="1"/>
     </row>
-    <row r="201" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="201" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A201" s="4" t="s">
         <v>223</v>
       </c>
@@ -13602,7 +13601,7 @@
       <c r="AG201" s="1"/>
       <c r="AH201" s="1"/>
     </row>
-    <row r="202" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="202" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A202" s="4" t="s">
         <v>224</v>
       </c>
@@ -13660,7 +13659,7 @@
       <c r="AG202" s="1"/>
       <c r="AH202" s="1"/>
     </row>
-    <row r="203" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="203" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A203" s="4" t="s">
         <v>225</v>
       </c>
@@ -13718,7 +13717,7 @@
       <c r="AG203" s="1"/>
       <c r="AH203" s="1"/>
     </row>
-    <row r="204" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="204" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A204" s="4" t="s">
         <v>226</v>
       </c>
@@ -13776,7 +13775,7 @@
       <c r="AG204" s="1"/>
       <c r="AH204" s="1"/>
     </row>
-    <row r="205" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="205" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A205" s="4" t="s">
         <v>227</v>
       </c>
@@ -13834,7 +13833,7 @@
       <c r="AG205" s="1"/>
       <c r="AH205" s="1"/>
     </row>
-    <row r="206" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="206" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A206" s="4" t="s">
         <v>228</v>
       </c>
@@ -13866,13 +13865,13 @@
       <c r="J206" s="26"/>
       <c r="K206" s="26"/>
       <c r="L206" s="26"/>
-      <c r="M206" s="31">
+      <c r="M206" s="36">
         <v>59510</v>
       </c>
-      <c r="N206" s="32">
+      <c r="N206" s="39">
         <v>1.8320000000000001</v>
       </c>
-      <c r="O206" s="33">
+      <c r="O206" s="40">
         <v>0.44</v>
       </c>
       <c r="P206" s="23">
@@ -13904,7 +13903,7 @@
       <c r="AG206" s="1"/>
       <c r="AH206" s="1"/>
     </row>
-    <row r="207" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="207" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A207" s="15" t="s">
         <v>229</v>
       </c>
@@ -13936,8 +13935,8 @@
       <c r="J207" s="24"/>
       <c r="K207" s="24"/>
       <c r="L207" s="24"/>
-      <c r="M207" s="29"/>
-      <c r="N207" s="29"/>
+      <c r="M207" s="37"/>
+      <c r="N207" s="37"/>
       <c r="O207" s="24"/>
       <c r="P207" s="24"/>
       <c r="Q207" s="24"/>
@@ -13962,7 +13961,7 @@
       <c r="AG207" s="1"/>
       <c r="AH207" s="1"/>
     </row>
-    <row r="208" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="208" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A208" s="15" t="s">
         <v>230</v>
       </c>
@@ -13994,8 +13993,8 @@
       <c r="J208" s="24"/>
       <c r="K208" s="24"/>
       <c r="L208" s="24"/>
-      <c r="M208" s="29"/>
-      <c r="N208" s="29"/>
+      <c r="M208" s="37"/>
+      <c r="N208" s="37"/>
       <c r="O208" s="24"/>
       <c r="P208" s="24"/>
       <c r="Q208" s="24"/>
@@ -14020,7 +14019,7 @@
       <c r="AG208" s="1"/>
       <c r="AH208" s="1"/>
     </row>
-    <row r="209" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="209" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A209" s="15" t="s">
         <v>231</v>
       </c>
@@ -14052,8 +14051,8 @@
       <c r="J209" s="24"/>
       <c r="K209" s="24"/>
       <c r="L209" s="24"/>
-      <c r="M209" s="29"/>
-      <c r="N209" s="29"/>
+      <c r="M209" s="37"/>
+      <c r="N209" s="37"/>
       <c r="O209" s="24"/>
       <c r="P209" s="24"/>
       <c r="Q209" s="24"/>
@@ -14078,7 +14077,7 @@
       <c r="AG209" s="1"/>
       <c r="AH209" s="1"/>
     </row>
-    <row r="210" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="210" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A210" s="15" t="s">
         <v>232</v>
       </c>
@@ -14110,8 +14109,8 @@
       <c r="J210" s="24"/>
       <c r="K210" s="24"/>
       <c r="L210" s="24"/>
-      <c r="M210" s="29"/>
-      <c r="N210" s="29"/>
+      <c r="M210" s="37"/>
+      <c r="N210" s="37"/>
       <c r="O210" s="24"/>
       <c r="P210" s="24"/>
       <c r="Q210" s="24"/>
@@ -14136,7 +14135,7 @@
       <c r="AG210" s="1"/>
       <c r="AH210" s="1"/>
     </row>
-    <row r="211" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="211" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A211" s="15" t="s">
         <v>233</v>
       </c>
@@ -14168,8 +14167,8 @@
       <c r="J211" s="24"/>
       <c r="K211" s="24"/>
       <c r="L211" s="24"/>
-      <c r="M211" s="29"/>
-      <c r="N211" s="29"/>
+      <c r="M211" s="37"/>
+      <c r="N211" s="37"/>
       <c r="O211" s="24"/>
       <c r="P211" s="24"/>
       <c r="Q211" s="24"/>
@@ -14194,7 +14193,7 @@
       <c r="AG211" s="1"/>
       <c r="AH211" s="1"/>
     </row>
-    <row r="212" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="212" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A212" s="15" t="s">
         <v>234</v>
       </c>
@@ -14226,8 +14225,8 @@
       <c r="J212" s="24"/>
       <c r="K212" s="24"/>
       <c r="L212" s="24"/>
-      <c r="M212" s="29"/>
-      <c r="N212" s="29"/>
+      <c r="M212" s="37"/>
+      <c r="N212" s="37"/>
       <c r="O212" s="24"/>
       <c r="P212" s="24"/>
       <c r="Q212" s="24"/>
@@ -14252,7 +14251,7 @@
       <c r="AG212" s="1"/>
       <c r="AH212" s="1"/>
     </row>
-    <row r="213" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="213" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A213" s="15" t="s">
         <v>235</v>
       </c>
@@ -14284,8 +14283,8 @@
       <c r="J213" s="24"/>
       <c r="K213" s="24"/>
       <c r="L213" s="24"/>
-      <c r="M213" s="29"/>
-      <c r="N213" s="29"/>
+      <c r="M213" s="37"/>
+      <c r="N213" s="37"/>
       <c r="O213" s="24"/>
       <c r="P213" s="24"/>
       <c r="Q213" s="24"/>
@@ -14310,7 +14309,7 @@
       <c r="AG213" s="1"/>
       <c r="AH213" s="1"/>
     </row>
-    <row r="214" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="214" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A214" s="15" t="s">
         <v>236</v>
       </c>
@@ -14342,8 +14341,8 @@
       <c r="J214" s="24"/>
       <c r="K214" s="24"/>
       <c r="L214" s="24"/>
-      <c r="M214" s="29"/>
-      <c r="N214" s="29"/>
+      <c r="M214" s="37"/>
+      <c r="N214" s="37"/>
       <c r="O214" s="24"/>
       <c r="P214" s="24"/>
       <c r="Q214" s="24"/>
@@ -14368,7 +14367,7 @@
       <c r="AG214" s="1"/>
       <c r="AH214" s="1"/>
     </row>
-    <row r="215" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="215" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A215" s="15" t="s">
         <v>237</v>
       </c>
@@ -14400,8 +14399,8 @@
       <c r="J215" s="24"/>
       <c r="K215" s="24"/>
       <c r="L215" s="24"/>
-      <c r="M215" s="29"/>
-      <c r="N215" s="29"/>
+      <c r="M215" s="37"/>
+      <c r="N215" s="37"/>
       <c r="O215" s="24"/>
       <c r="P215" s="24"/>
       <c r="Q215" s="24"/>
@@ -14426,7 +14425,7 @@
       <c r="AG215" s="1"/>
       <c r="AH215" s="1"/>
     </row>
-    <row r="216" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="216" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A216" s="15" t="s">
         <v>238</v>
       </c>
@@ -14458,8 +14457,8 @@
       <c r="J216" s="24"/>
       <c r="K216" s="24"/>
       <c r="L216" s="24"/>
-      <c r="M216" s="29"/>
-      <c r="N216" s="29"/>
+      <c r="M216" s="37"/>
+      <c r="N216" s="37"/>
       <c r="O216" s="24"/>
       <c r="P216" s="24"/>
       <c r="Q216" s="24"/>
@@ -14484,7 +14483,7 @@
       <c r="AG216" s="1"/>
       <c r="AH216" s="1"/>
     </row>
-    <row r="217" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="217" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A217" s="15" t="s">
         <v>239</v>
       </c>
@@ -14516,8 +14515,8 @@
       <c r="J217" s="25"/>
       <c r="K217" s="25"/>
       <c r="L217" s="25"/>
-      <c r="M217" s="30"/>
-      <c r="N217" s="30"/>
+      <c r="M217" s="38"/>
+      <c r="N217" s="38"/>
       <c r="O217" s="25"/>
       <c r="P217" s="25"/>
       <c r="Q217" s="25"/>
@@ -14571,7 +14570,7 @@
       <c r="I218" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J218" s="28">
+      <c r="J218" s="41">
         <v>43.1</v>
       </c>
       <c r="K218" s="26">
@@ -14580,7 +14579,7 @@
       <c r="L218" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="M218" s="27">
+      <c r="M218" s="35">
         <v>56100</v>
       </c>
       <c r="N218" s="26">
@@ -14647,7 +14646,7 @@
       <c r="I219" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J219" s="29"/>
+      <c r="J219" s="37"/>
       <c r="K219" s="24"/>
       <c r="L219" s="24"/>
       <c r="M219" s="24"/>
@@ -14705,7 +14704,7 @@
       <c r="I220" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J220" s="29"/>
+      <c r="J220" s="37"/>
       <c r="K220" s="24"/>
       <c r="L220" s="24"/>
       <c r="M220" s="24"/>
@@ -14763,7 +14762,7 @@
       <c r="I221" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J221" s="29"/>
+      <c r="J221" s="37"/>
       <c r="K221" s="24"/>
       <c r="L221" s="24"/>
       <c r="M221" s="24"/>
@@ -14821,7 +14820,7 @@
       <c r="I222" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J222" s="29"/>
+      <c r="J222" s="37"/>
       <c r="K222" s="24"/>
       <c r="L222" s="24"/>
       <c r="M222" s="24"/>
@@ -14879,7 +14878,7 @@
       <c r="I223" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J223" s="29"/>
+      <c r="J223" s="37"/>
       <c r="K223" s="24"/>
       <c r="L223" s="24"/>
       <c r="M223" s="24"/>
@@ -14937,7 +14936,7 @@
       <c r="I224" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J224" s="29"/>
+      <c r="J224" s="37"/>
       <c r="K224" s="24"/>
       <c r="L224" s="24"/>
       <c r="M224" s="24"/>
@@ -14995,7 +14994,7 @@
       <c r="I225" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J225" s="29"/>
+      <c r="J225" s="37"/>
       <c r="K225" s="24"/>
       <c r="L225" s="24"/>
       <c r="M225" s="24"/>
@@ -15053,7 +15052,7 @@
       <c r="I226" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J226" s="29"/>
+      <c r="J226" s="37"/>
       <c r="K226" s="24"/>
       <c r="L226" s="24"/>
       <c r="M226" s="24"/>
@@ -15111,7 +15110,7 @@
       <c r="I227" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J227" s="29"/>
+      <c r="J227" s="37"/>
       <c r="K227" s="24"/>
       <c r="L227" s="24"/>
       <c r="M227" s="24"/>
@@ -15169,7 +15168,7 @@
       <c r="I228" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J228" s="29"/>
+      <c r="J228" s="37"/>
       <c r="K228" s="24"/>
       <c r="L228" s="24"/>
       <c r="M228" s="24"/>
@@ -15227,7 +15226,7 @@
       <c r="I229" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="J229" s="30"/>
+      <c r="J229" s="38"/>
       <c r="K229" s="25"/>
       <c r="L229" s="25"/>
       <c r="M229" s="25"/>
@@ -15256,7 +15255,7 @@
       <c r="AG229" s="1"/>
       <c r="AH229" s="1"/>
     </row>
-    <row r="230" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="230" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A230" s="4" t="s">
         <v>252</v>
       </c>
@@ -15294,13 +15293,13 @@
       <c r="L230" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="M230" s="27">
+      <c r="M230" s="35">
         <v>69300</v>
       </c>
-      <c r="N230" s="27">
+      <c r="N230" s="35">
         <v>25</v>
       </c>
-      <c r="O230" s="27">
+      <c r="O230" s="35">
         <v>8</v>
       </c>
       <c r="P230" s="23">
@@ -15332,7 +15331,7 @@
       <c r="AG230" s="1"/>
       <c r="AH230" s="1"/>
     </row>
-    <row r="231" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="231" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A231" s="4" t="s">
         <v>253</v>
       </c>
@@ -15390,7 +15389,7 @@
       <c r="AG231" s="1"/>
       <c r="AH231" s="1"/>
     </row>
-    <row r="232" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="232" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A232" s="4" t="s">
         <v>254</v>
       </c>
@@ -15448,7 +15447,7 @@
       <c r="AG232" s="1"/>
       <c r="AH232" s="1"/>
     </row>
-    <row r="233" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="233" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A233" s="4" t="s">
         <v>255</v>
       </c>
@@ -15506,7 +15505,7 @@
       <c r="AG233" s="1"/>
       <c r="AH233" s="1"/>
     </row>
-    <row r="234" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="234" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A234" s="4" t="s">
         <v>256</v>
       </c>
@@ -15564,7 +15563,7 @@
       <c r="AG234" s="1"/>
       <c r="AH234" s="1"/>
     </row>
-    <row r="235" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="235" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A235" s="4" t="s">
         <v>257</v>
       </c>
@@ -15622,7 +15621,7 @@
       <c r="AG235" s="1"/>
       <c r="AH235" s="1"/>
     </row>
-    <row r="236" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="236" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A236" s="4" t="s">
         <v>258</v>
       </c>
@@ -15680,7 +15679,7 @@
       <c r="AG236" s="1"/>
       <c r="AH236" s="1"/>
     </row>
-    <row r="237" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="237" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A237" s="4" t="s">
         <v>259</v>
       </c>
@@ -15738,7 +15737,7 @@
       <c r="AG237" s="1"/>
       <c r="AH237" s="1"/>
     </row>
-    <row r="238" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="238" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A238" s="4" t="s">
         <v>260</v>
       </c>
@@ -15796,7 +15795,7 @@
       <c r="AG238" s="1"/>
       <c r="AH238" s="1"/>
     </row>
-    <row r="239" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="239" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A239" s="4" t="s">
         <v>261</v>
       </c>
@@ -15854,7 +15853,7 @@
       <c r="AG239" s="1"/>
       <c r="AH239" s="1"/>
     </row>
-    <row r="240" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="240" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A240" s="4" t="s">
         <v>262</v>
       </c>
@@ -15912,7 +15911,7 @@
       <c r="AG240" s="1"/>
       <c r="AH240" s="1"/>
     </row>
-    <row r="241" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="241" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A241" s="4" t="s">
         <v>263</v>
       </c>
@@ -15970,7 +15969,7 @@
       <c r="AG241" s="1"/>
       <c r="AH241" s="1"/>
     </row>
-    <row r="242" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="242" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A242" s="4" t="s">
         <v>264</v>
       </c>
@@ -16006,18 +16005,18 @@
       <c r="L242" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="M242" s="34">
+      <c r="M242" s="27">
         <v>0.2</v>
       </c>
-      <c r="N242" s="34" t="s">
+      <c r="N242" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="O242" s="37">
+      <c r="O242" s="30">
         <v>23900</v>
       </c>
-      <c r="P242" s="40"/>
-      <c r="Q242" s="41"/>
-      <c r="R242" s="41"/>
+      <c r="P242" s="33"/>
+      <c r="Q242" s="34"/>
+      <c r="R242" s="34"/>
       <c r="S242" s="13">
         <f t="shared" ref="S242:S253" si="38">H242*$K$242*$M$242*$O$242</f>
         <v>0</v>
@@ -16038,7 +16037,7 @@
       <c r="AG242" s="1"/>
       <c r="AH242" s="1"/>
     </row>
-    <row r="243" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="243" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A243" s="4" t="s">
         <v>265</v>
       </c>
@@ -16070,12 +16069,12 @@
       <c r="J243" s="24"/>
       <c r="K243" s="24"/>
       <c r="L243" s="24"/>
-      <c r="M243" s="35"/>
-      <c r="N243" s="35"/>
-      <c r="O243" s="38"/>
-      <c r="P243" s="38"/>
-      <c r="Q243" s="38"/>
-      <c r="R243" s="38"/>
+      <c r="M243" s="28"/>
+      <c r="N243" s="28"/>
+      <c r="O243" s="31"/>
+      <c r="P243" s="31"/>
+      <c r="Q243" s="31"/>
+      <c r="R243" s="31"/>
       <c r="S243" s="13">
         <f t="shared" si="38"/>
         <v>0</v>
@@ -16096,7 +16095,7 @@
       <c r="AG243" s="1"/>
       <c r="AH243" s="1"/>
     </row>
-    <row r="244" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="244" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A244" s="4" t="s">
         <v>266</v>
       </c>
@@ -16128,12 +16127,12 @@
       <c r="J244" s="24"/>
       <c r="K244" s="24"/>
       <c r="L244" s="24"/>
-      <c r="M244" s="35"/>
-      <c r="N244" s="35"/>
-      <c r="O244" s="38"/>
-      <c r="P244" s="38"/>
-      <c r="Q244" s="38"/>
-      <c r="R244" s="38"/>
+      <c r="M244" s="28"/>
+      <c r="N244" s="28"/>
+      <c r="O244" s="31"/>
+      <c r="P244" s="31"/>
+      <c r="Q244" s="31"/>
+      <c r="R244" s="31"/>
       <c r="S244" s="13">
         <f t="shared" si="38"/>
         <v>0</v>
@@ -16154,7 +16153,7 @@
       <c r="AG244" s="1"/>
       <c r="AH244" s="1"/>
     </row>
-    <row r="245" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="245" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A245" s="4" t="s">
         <v>267</v>
       </c>
@@ -16186,12 +16185,12 @@
       <c r="J245" s="24"/>
       <c r="K245" s="24"/>
       <c r="L245" s="24"/>
-      <c r="M245" s="35"/>
-      <c r="N245" s="35"/>
-      <c r="O245" s="38"/>
-      <c r="P245" s="38"/>
-      <c r="Q245" s="38"/>
-      <c r="R245" s="38"/>
+      <c r="M245" s="28"/>
+      <c r="N245" s="28"/>
+      <c r="O245" s="31"/>
+      <c r="P245" s="31"/>
+      <c r="Q245" s="31"/>
+      <c r="R245" s="31"/>
       <c r="S245" s="13">
         <f t="shared" si="38"/>
         <v>0</v>
@@ -16212,7 +16211,7 @@
       <c r="AG245" s="1"/>
       <c r="AH245" s="1"/>
     </row>
-    <row r="246" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="246" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A246" s="4" t="s">
         <v>268</v>
       </c>
@@ -16244,12 +16243,12 @@
       <c r="J246" s="24"/>
       <c r="K246" s="24"/>
       <c r="L246" s="24"/>
-      <c r="M246" s="35"/>
-      <c r="N246" s="35"/>
-      <c r="O246" s="38"/>
-      <c r="P246" s="38"/>
-      <c r="Q246" s="38"/>
-      <c r="R246" s="38"/>
+      <c r="M246" s="28"/>
+      <c r="N246" s="28"/>
+      <c r="O246" s="31"/>
+      <c r="P246" s="31"/>
+      <c r="Q246" s="31"/>
+      <c r="R246" s="31"/>
       <c r="S246" s="13">
         <f t="shared" si="38"/>
         <v>0</v>
@@ -16270,7 +16269,7 @@
       <c r="AG246" s="1"/>
       <c r="AH246" s="1"/>
     </row>
-    <row r="247" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="247" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A247" s="4" t="s">
         <v>269</v>
       </c>
@@ -16302,12 +16301,12 @@
       <c r="J247" s="24"/>
       <c r="K247" s="24"/>
       <c r="L247" s="24"/>
-      <c r="M247" s="35"/>
-      <c r="N247" s="35"/>
-      <c r="O247" s="38"/>
-      <c r="P247" s="38"/>
-      <c r="Q247" s="38"/>
-      <c r="R247" s="38"/>
+      <c r="M247" s="28"/>
+      <c r="N247" s="28"/>
+      <c r="O247" s="31"/>
+      <c r="P247" s="31"/>
+      <c r="Q247" s="31"/>
+      <c r="R247" s="31"/>
       <c r="S247" s="13">
         <f t="shared" si="38"/>
         <v>0</v>
@@ -16328,7 +16327,7 @@
       <c r="AG247" s="1"/>
       <c r="AH247" s="1"/>
     </row>
-    <row r="248" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="248" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A248" s="4" t="s">
         <v>270</v>
       </c>
@@ -16360,12 +16359,12 @@
       <c r="J248" s="24"/>
       <c r="K248" s="24"/>
       <c r="L248" s="24"/>
-      <c r="M248" s="35"/>
-      <c r="N248" s="35"/>
-      <c r="O248" s="38"/>
-      <c r="P248" s="38"/>
-      <c r="Q248" s="38"/>
-      <c r="R248" s="38"/>
+      <c r="M248" s="28"/>
+      <c r="N248" s="28"/>
+      <c r="O248" s="31"/>
+      <c r="P248" s="31"/>
+      <c r="Q248" s="31"/>
+      <c r="R248" s="31"/>
       <c r="S248" s="13">
         <f t="shared" si="38"/>
         <v>0</v>
@@ -16386,7 +16385,7 @@
       <c r="AG248" s="1"/>
       <c r="AH248" s="1"/>
     </row>
-    <row r="249" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="249" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A249" s="4" t="s">
         <v>271</v>
       </c>
@@ -16418,12 +16417,12 @@
       <c r="J249" s="24"/>
       <c r="K249" s="24"/>
       <c r="L249" s="24"/>
-      <c r="M249" s="35"/>
-      <c r="N249" s="35"/>
-      <c r="O249" s="38"/>
-      <c r="P249" s="38"/>
-      <c r="Q249" s="38"/>
-      <c r="R249" s="38"/>
+      <c r="M249" s="28"/>
+      <c r="N249" s="28"/>
+      <c r="O249" s="31"/>
+      <c r="P249" s="31"/>
+      <c r="Q249" s="31"/>
+      <c r="R249" s="31"/>
       <c r="S249" s="13">
         <f t="shared" si="38"/>
         <v>0</v>
@@ -16444,7 +16443,7 @@
       <c r="AG249" s="1"/>
       <c r="AH249" s="1"/>
     </row>
-    <row r="250" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="250" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A250" s="4" t="s">
         <v>272</v>
       </c>
@@ -16476,12 +16475,12 @@
       <c r="J250" s="24"/>
       <c r="K250" s="24"/>
       <c r="L250" s="24"/>
-      <c r="M250" s="35"/>
-      <c r="N250" s="35"/>
-      <c r="O250" s="38"/>
-      <c r="P250" s="38"/>
-      <c r="Q250" s="38"/>
-      <c r="R250" s="38"/>
+      <c r="M250" s="28"/>
+      <c r="N250" s="28"/>
+      <c r="O250" s="31"/>
+      <c r="P250" s="31"/>
+      <c r="Q250" s="31"/>
+      <c r="R250" s="31"/>
       <c r="S250" s="13">
         <f t="shared" si="38"/>
         <v>0</v>
@@ -16502,7 +16501,7 @@
       <c r="AG250" s="1"/>
       <c r="AH250" s="1"/>
     </row>
-    <row r="251" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="251" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A251" s="4" t="s">
         <v>273</v>
       </c>
@@ -16534,12 +16533,12 @@
       <c r="J251" s="24"/>
       <c r="K251" s="24"/>
       <c r="L251" s="24"/>
-      <c r="M251" s="35"/>
-      <c r="N251" s="35"/>
-      <c r="O251" s="38"/>
-      <c r="P251" s="38"/>
-      <c r="Q251" s="38"/>
-      <c r="R251" s="38"/>
+      <c r="M251" s="28"/>
+      <c r="N251" s="28"/>
+      <c r="O251" s="31"/>
+      <c r="P251" s="31"/>
+      <c r="Q251" s="31"/>
+      <c r="R251" s="31"/>
       <c r="S251" s="13">
         <f t="shared" si="38"/>
         <v>0</v>
@@ -16560,7 +16559,7 @@
       <c r="AG251" s="1"/>
       <c r="AH251" s="1"/>
     </row>
-    <row r="252" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="252" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A252" s="4" t="s">
         <v>274</v>
       </c>
@@ -16592,12 +16591,12 @@
       <c r="J252" s="24"/>
       <c r="K252" s="24"/>
       <c r="L252" s="24"/>
-      <c r="M252" s="35"/>
-      <c r="N252" s="35"/>
-      <c r="O252" s="38"/>
-      <c r="P252" s="38"/>
-      <c r="Q252" s="38"/>
-      <c r="R252" s="38"/>
+      <c r="M252" s="28"/>
+      <c r="N252" s="28"/>
+      <c r="O252" s="31"/>
+      <c r="P252" s="31"/>
+      <c r="Q252" s="31"/>
+      <c r="R252" s="31"/>
       <c r="S252" s="13">
         <f t="shared" si="38"/>
         <v>0</v>
@@ -16618,7 +16617,7 @@
       <c r="AG252" s="1"/>
       <c r="AH252" s="1"/>
     </row>
-    <row r="253" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="253" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A253" s="4" t="s">
         <v>275</v>
       </c>
@@ -16650,12 +16649,12 @@
       <c r="J253" s="25"/>
       <c r="K253" s="25"/>
       <c r="L253" s="25"/>
-      <c r="M253" s="36"/>
-      <c r="N253" s="35"/>
-      <c r="O253" s="39"/>
-      <c r="P253" s="38"/>
-      <c r="Q253" s="38"/>
-      <c r="R253" s="38"/>
+      <c r="M253" s="29"/>
+      <c r="N253" s="28"/>
+      <c r="O253" s="32"/>
+      <c r="P253" s="31"/>
+      <c r="Q253" s="31"/>
+      <c r="R253" s="31"/>
       <c r="S253" s="13">
         <f t="shared" si="38"/>
         <v>0</v>
@@ -16676,7 +16675,7 @@
       <c r="AG253" s="1"/>
       <c r="AH253" s="1"/>
     </row>
-    <row r="254" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="254" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A254" s="4" t="s">
         <v>276</v>
       </c>
@@ -16712,18 +16711,18 @@
       <c r="L254" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="M254" s="34">
+      <c r="M254" s="27">
         <v>0.4</v>
       </c>
-      <c r="N254" s="34" t="s">
+      <c r="N254" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="O254" s="37">
+      <c r="O254" s="30">
         <v>11700</v>
       </c>
-      <c r="P254" s="40"/>
-      <c r="Q254" s="41"/>
-      <c r="R254" s="41"/>
+      <c r="P254" s="33"/>
+      <c r="Q254" s="34"/>
+      <c r="R254" s="34"/>
       <c r="S254" s="7">
         <f t="shared" ref="S254:S265" si="39">H254*$K$254*$M$254*$O$254</f>
         <v>0</v>
@@ -16744,7 +16743,7 @@
       <c r="AG254" s="1"/>
       <c r="AH254" s="1"/>
     </row>
-    <row r="255" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="255" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A255" s="4" t="s">
         <v>277</v>
       </c>
@@ -16776,12 +16775,12 @@
       <c r="J255" s="24"/>
       <c r="K255" s="24"/>
       <c r="L255" s="24"/>
-      <c r="M255" s="35"/>
-      <c r="N255" s="35"/>
-      <c r="O255" s="38"/>
-      <c r="P255" s="38"/>
-      <c r="Q255" s="38"/>
-      <c r="R255" s="38"/>
+      <c r="M255" s="28"/>
+      <c r="N255" s="28"/>
+      <c r="O255" s="31"/>
+      <c r="P255" s="31"/>
+      <c r="Q255" s="31"/>
+      <c r="R255" s="31"/>
       <c r="S255" s="7">
         <f t="shared" si="39"/>
         <v>0</v>
@@ -16802,7 +16801,7 @@
       <c r="AG255" s="1"/>
       <c r="AH255" s="1"/>
     </row>
-    <row r="256" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="256" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A256" s="4" t="s">
         <v>278</v>
       </c>
@@ -16834,12 +16833,12 @@
       <c r="J256" s="24"/>
       <c r="K256" s="24"/>
       <c r="L256" s="24"/>
-      <c r="M256" s="35"/>
-      <c r="N256" s="35"/>
-      <c r="O256" s="38"/>
-      <c r="P256" s="38"/>
-      <c r="Q256" s="38"/>
-      <c r="R256" s="38"/>
+      <c r="M256" s="28"/>
+      <c r="N256" s="28"/>
+      <c r="O256" s="31"/>
+      <c r="P256" s="31"/>
+      <c r="Q256" s="31"/>
+      <c r="R256" s="31"/>
       <c r="S256" s="7">
         <f t="shared" si="39"/>
         <v>0</v>
@@ -16860,7 +16859,7 @@
       <c r="AG256" s="1"/>
       <c r="AH256" s="1"/>
     </row>
-    <row r="257" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="257" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A257" s="4" t="s">
         <v>279</v>
       </c>
@@ -16892,12 +16891,12 @@
       <c r="J257" s="24"/>
       <c r="K257" s="24"/>
       <c r="L257" s="24"/>
-      <c r="M257" s="35"/>
-      <c r="N257" s="35"/>
-      <c r="O257" s="38"/>
-      <c r="P257" s="38"/>
-      <c r="Q257" s="38"/>
-      <c r="R257" s="38"/>
+      <c r="M257" s="28"/>
+      <c r="N257" s="28"/>
+      <c r="O257" s="31"/>
+      <c r="P257" s="31"/>
+      <c r="Q257" s="31"/>
+      <c r="R257" s="31"/>
       <c r="S257" s="7">
         <f t="shared" si="39"/>
         <v>0</v>
@@ -16918,7 +16917,7 @@
       <c r="AG257" s="1"/>
       <c r="AH257" s="1"/>
     </row>
-    <row r="258" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="258" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A258" s="4" t="s">
         <v>280</v>
       </c>
@@ -16950,12 +16949,12 @@
       <c r="J258" s="24"/>
       <c r="K258" s="24"/>
       <c r="L258" s="24"/>
-      <c r="M258" s="35"/>
-      <c r="N258" s="35"/>
-      <c r="O258" s="38"/>
-      <c r="P258" s="38"/>
-      <c r="Q258" s="38"/>
-      <c r="R258" s="38"/>
+      <c r="M258" s="28"/>
+      <c r="N258" s="28"/>
+      <c r="O258" s="31"/>
+      <c r="P258" s="31"/>
+      <c r="Q258" s="31"/>
+      <c r="R258" s="31"/>
       <c r="S258" s="7">
         <f t="shared" si="39"/>
         <v>0</v>
@@ -16976,7 +16975,7 @@
       <c r="AG258" s="1"/>
       <c r="AH258" s="1"/>
     </row>
-    <row r="259" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="259" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A259" s="4" t="s">
         <v>281</v>
       </c>
@@ -17008,12 +17007,12 @@
       <c r="J259" s="24"/>
       <c r="K259" s="24"/>
       <c r="L259" s="24"/>
-      <c r="M259" s="35"/>
-      <c r="N259" s="35"/>
-      <c r="O259" s="38"/>
-      <c r="P259" s="38"/>
-      <c r="Q259" s="38"/>
-      <c r="R259" s="38"/>
+      <c r="M259" s="28"/>
+      <c r="N259" s="28"/>
+      <c r="O259" s="31"/>
+      <c r="P259" s="31"/>
+      <c r="Q259" s="31"/>
+      <c r="R259" s="31"/>
       <c r="S259" s="7">
         <f t="shared" si="39"/>
         <v>0</v>
@@ -17034,7 +17033,7 @@
       <c r="AG259" s="1"/>
       <c r="AH259" s="1"/>
     </row>
-    <row r="260" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="260" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A260" s="4" t="s">
         <v>282</v>
       </c>
@@ -17066,12 +17065,12 @@
       <c r="J260" s="24"/>
       <c r="K260" s="24"/>
       <c r="L260" s="24"/>
-      <c r="M260" s="35"/>
-      <c r="N260" s="35"/>
-      <c r="O260" s="38"/>
-      <c r="P260" s="38"/>
-      <c r="Q260" s="38"/>
-      <c r="R260" s="38"/>
+      <c r="M260" s="28"/>
+      <c r="N260" s="28"/>
+      <c r="O260" s="31"/>
+      <c r="P260" s="31"/>
+      <c r="Q260" s="31"/>
+      <c r="R260" s="31"/>
       <c r="S260" s="7">
         <f t="shared" si="39"/>
         <v>0</v>
@@ -17092,7 +17091,7 @@
       <c r="AG260" s="1"/>
       <c r="AH260" s="1"/>
     </row>
-    <row r="261" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="261" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A261" s="4" t="s">
         <v>283</v>
       </c>
@@ -17124,12 +17123,12 @@
       <c r="J261" s="24"/>
       <c r="K261" s="24"/>
       <c r="L261" s="24"/>
-      <c r="M261" s="35"/>
-      <c r="N261" s="35"/>
-      <c r="O261" s="38"/>
-      <c r="P261" s="38"/>
-      <c r="Q261" s="38"/>
-      <c r="R261" s="38"/>
+      <c r="M261" s="28"/>
+      <c r="N261" s="28"/>
+      <c r="O261" s="31"/>
+      <c r="P261" s="31"/>
+      <c r="Q261" s="31"/>
+      <c r="R261" s="31"/>
       <c r="S261" s="7">
         <f t="shared" si="39"/>
         <v>0</v>
@@ -17150,7 +17149,7 @@
       <c r="AG261" s="1"/>
       <c r="AH261" s="1"/>
     </row>
-    <row r="262" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="262" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A262" s="4" t="s">
         <v>284</v>
       </c>
@@ -17182,12 +17181,12 @@
       <c r="J262" s="24"/>
       <c r="K262" s="24"/>
       <c r="L262" s="24"/>
-      <c r="M262" s="35"/>
-      <c r="N262" s="35"/>
-      <c r="O262" s="38"/>
-      <c r="P262" s="38"/>
-      <c r="Q262" s="38"/>
-      <c r="R262" s="38"/>
+      <c r="M262" s="28"/>
+      <c r="N262" s="28"/>
+      <c r="O262" s="31"/>
+      <c r="P262" s="31"/>
+      <c r="Q262" s="31"/>
+      <c r="R262" s="31"/>
       <c r="S262" s="7">
         <f t="shared" si="39"/>
         <v>0</v>
@@ -17208,7 +17207,7 @@
       <c r="AG262" s="1"/>
       <c r="AH262" s="1"/>
     </row>
-    <row r="263" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="263" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A263" s="4" t="s">
         <v>285</v>
       </c>
@@ -17240,12 +17239,12 @@
       <c r="J263" s="24"/>
       <c r="K263" s="24"/>
       <c r="L263" s="24"/>
-      <c r="M263" s="35"/>
-      <c r="N263" s="35"/>
-      <c r="O263" s="38"/>
-      <c r="P263" s="38"/>
-      <c r="Q263" s="38"/>
-      <c r="R263" s="38"/>
+      <c r="M263" s="28"/>
+      <c r="N263" s="28"/>
+      <c r="O263" s="31"/>
+      <c r="P263" s="31"/>
+      <c r="Q263" s="31"/>
+      <c r="R263" s="31"/>
       <c r="S263" s="7">
         <f t="shared" si="39"/>
         <v>0</v>
@@ -17266,7 +17265,7 @@
       <c r="AG263" s="1"/>
       <c r="AH263" s="1"/>
     </row>
-    <row r="264" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="264" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A264" s="4" t="s">
         <v>286</v>
       </c>
@@ -17298,12 +17297,12 @@
       <c r="J264" s="24"/>
       <c r="K264" s="24"/>
       <c r="L264" s="24"/>
-      <c r="M264" s="35"/>
-      <c r="N264" s="35"/>
-      <c r="O264" s="38"/>
-      <c r="P264" s="38"/>
-      <c r="Q264" s="38"/>
-      <c r="R264" s="38"/>
+      <c r="M264" s="28"/>
+      <c r="N264" s="28"/>
+      <c r="O264" s="31"/>
+      <c r="P264" s="31"/>
+      <c r="Q264" s="31"/>
+      <c r="R264" s="31"/>
       <c r="S264" s="7">
         <f t="shared" si="39"/>
         <v>0</v>
@@ -17324,7 +17323,7 @@
       <c r="AG264" s="1"/>
       <c r="AH264" s="1"/>
     </row>
-    <row r="265" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="265" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A265" s="4" t="s">
         <v>287</v>
       </c>
@@ -17356,12 +17355,12 @@
       <c r="J265" s="25"/>
       <c r="K265" s="25"/>
       <c r="L265" s="25"/>
-      <c r="M265" s="36"/>
-      <c r="N265" s="35"/>
-      <c r="O265" s="39"/>
-      <c r="P265" s="38"/>
-      <c r="Q265" s="38"/>
-      <c r="R265" s="38"/>
+      <c r="M265" s="29"/>
+      <c r="N265" s="28"/>
+      <c r="O265" s="32"/>
+      <c r="P265" s="31"/>
+      <c r="Q265" s="31"/>
+      <c r="R265" s="31"/>
       <c r="S265" s="7">
         <f t="shared" si="39"/>
         <v>0</v>
@@ -17382,7 +17381,7 @@
       <c r="AG265" s="1"/>
       <c r="AH265" s="1"/>
     </row>
-    <row r="266" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="266" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A266" s="4" t="s">
         <v>288</v>
       </c>
@@ -17456,7 +17455,7 @@
       <c r="AG266" s="1"/>
       <c r="AH266" s="1"/>
     </row>
-    <row r="267" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="267" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A267" s="4" t="s">
         <v>289</v>
       </c>
@@ -17514,7 +17513,7 @@
       <c r="AG267" s="1"/>
       <c r="AH267" s="1"/>
     </row>
-    <row r="268" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="268" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A268" s="4" t="s">
         <v>290</v>
       </c>
@@ -17572,7 +17571,7 @@
       <c r="AG268" s="1"/>
       <c r="AH268" s="1"/>
     </row>
-    <row r="269" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="269" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A269" s="4" t="s">
         <v>291</v>
       </c>
@@ -17630,7 +17629,7 @@
       <c r="AG269" s="1"/>
       <c r="AH269" s="1"/>
     </row>
-    <row r="270" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="270" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A270" s="4" t="s">
         <v>292</v>
       </c>
@@ -17688,7 +17687,7 @@
       <c r="AG270" s="1"/>
       <c r="AH270" s="1"/>
     </row>
-    <row r="271" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="271" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A271" s="4" t="s">
         <v>293</v>
       </c>
@@ -17746,7 +17745,7 @@
       <c r="AG271" s="1"/>
       <c r="AH271" s="1"/>
     </row>
-    <row r="272" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="272" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A272" s="4" t="s">
         <v>294</v>
       </c>
@@ -17804,7 +17803,7 @@
       <c r="AG272" s="1"/>
       <c r="AH272" s="1"/>
     </row>
-    <row r="273" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="273" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A273" s="4" t="s">
         <v>295</v>
       </c>
@@ -17862,7 +17861,7 @@
       <c r="AG273" s="1"/>
       <c r="AH273" s="1"/>
     </row>
-    <row r="274" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="274" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A274" s="4" t="s">
         <v>296</v>
       </c>
@@ -17920,7 +17919,7 @@
       <c r="AG274" s="1"/>
       <c r="AH274" s="1"/>
     </row>
-    <row r="275" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="275" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A275" s="4" t="s">
         <v>297</v>
       </c>
@@ -17978,7 +17977,7 @@
       <c r="AG275" s="1"/>
       <c r="AH275" s="1"/>
     </row>
-    <row r="276" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="276" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A276" s="4" t="s">
         <v>298</v>
       </c>
@@ -18036,7 +18035,7 @@
       <c r="AG276" s="1"/>
       <c r="AH276" s="1"/>
     </row>
-    <row r="277" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="277" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A277" s="4" t="s">
         <v>299</v>
       </c>
@@ -18094,7 +18093,7 @@
       <c r="AG277" s="1"/>
       <c r="AH277" s="1"/>
     </row>
-    <row r="278" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="278" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A278" s="4" t="s">
         <v>300</v>
       </c>
@@ -18126,13 +18125,13 @@
       <c r="J278" s="26"/>
       <c r="K278" s="26"/>
       <c r="L278" s="26"/>
-      <c r="M278" s="31">
+      <c r="M278" s="36">
         <v>59510</v>
       </c>
-      <c r="N278" s="32">
+      <c r="N278" s="39">
         <v>1.8320000000000001</v>
       </c>
-      <c r="O278" s="33">
+      <c r="O278" s="40">
         <v>0.44</v>
       </c>
       <c r="P278" s="23">
@@ -18164,7 +18163,7 @@
       <c r="AG278" s="1"/>
       <c r="AH278" s="1"/>
     </row>
-    <row r="279" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="279" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A279" s="15" t="s">
         <v>301</v>
       </c>
@@ -18196,8 +18195,8 @@
       <c r="J279" s="24"/>
       <c r="K279" s="24"/>
       <c r="L279" s="24"/>
-      <c r="M279" s="29"/>
-      <c r="N279" s="29"/>
+      <c r="M279" s="37"/>
+      <c r="N279" s="37"/>
       <c r="O279" s="24"/>
       <c r="P279" s="24"/>
       <c r="Q279" s="24"/>
@@ -18222,7 +18221,7 @@
       <c r="AG279" s="1"/>
       <c r="AH279" s="1"/>
     </row>
-    <row r="280" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="280" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A280" s="15" t="s">
         <v>302</v>
       </c>
@@ -18254,8 +18253,8 @@
       <c r="J280" s="24"/>
       <c r="K280" s="24"/>
       <c r="L280" s="24"/>
-      <c r="M280" s="29"/>
-      <c r="N280" s="29"/>
+      <c r="M280" s="37"/>
+      <c r="N280" s="37"/>
       <c r="O280" s="24"/>
       <c r="P280" s="24"/>
       <c r="Q280" s="24"/>
@@ -18280,7 +18279,7 @@
       <c r="AG280" s="1"/>
       <c r="AH280" s="1"/>
     </row>
-    <row r="281" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="281" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A281" s="15" t="s">
         <v>303</v>
       </c>
@@ -18312,8 +18311,8 @@
       <c r="J281" s="24"/>
       <c r="K281" s="24"/>
       <c r="L281" s="24"/>
-      <c r="M281" s="29"/>
-      <c r="N281" s="29"/>
+      <c r="M281" s="37"/>
+      <c r="N281" s="37"/>
       <c r="O281" s="24"/>
       <c r="P281" s="24"/>
       <c r="Q281" s="24"/>
@@ -18338,7 +18337,7 @@
       <c r="AG281" s="1"/>
       <c r="AH281" s="1"/>
     </row>
-    <row r="282" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="282" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A282" s="15" t="s">
         <v>304</v>
       </c>
@@ -18370,8 +18369,8 @@
       <c r="J282" s="24"/>
       <c r="K282" s="24"/>
       <c r="L282" s="24"/>
-      <c r="M282" s="29"/>
-      <c r="N282" s="29"/>
+      <c r="M282" s="37"/>
+      <c r="N282" s="37"/>
       <c r="O282" s="24"/>
       <c r="P282" s="24"/>
       <c r="Q282" s="24"/>
@@ -18396,7 +18395,7 @@
       <c r="AG282" s="1"/>
       <c r="AH282" s="1"/>
     </row>
-    <row r="283" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="283" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A283" s="15" t="s">
         <v>305</v>
       </c>
@@ -18428,8 +18427,8 @@
       <c r="J283" s="24"/>
       <c r="K283" s="24"/>
       <c r="L283" s="24"/>
-      <c r="M283" s="29"/>
-      <c r="N283" s="29"/>
+      <c r="M283" s="37"/>
+      <c r="N283" s="37"/>
       <c r="O283" s="24"/>
       <c r="P283" s="24"/>
       <c r="Q283" s="24"/>
@@ -18454,7 +18453,7 @@
       <c r="AG283" s="1"/>
       <c r="AH283" s="1"/>
     </row>
-    <row r="284" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="284" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A284" s="15" t="s">
         <v>306</v>
       </c>
@@ -18486,8 +18485,8 @@
       <c r="J284" s="24"/>
       <c r="K284" s="24"/>
       <c r="L284" s="24"/>
-      <c r="M284" s="29"/>
-      <c r="N284" s="29"/>
+      <c r="M284" s="37"/>
+      <c r="N284" s="37"/>
       <c r="O284" s="24"/>
       <c r="P284" s="24"/>
       <c r="Q284" s="24"/>
@@ -18512,7 +18511,7 @@
       <c r="AG284" s="1"/>
       <c r="AH284" s="1"/>
     </row>
-    <row r="285" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="285" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A285" s="15" t="s">
         <v>307</v>
       </c>
@@ -18544,8 +18543,8 @@
       <c r="J285" s="24"/>
       <c r="K285" s="24"/>
       <c r="L285" s="24"/>
-      <c r="M285" s="29"/>
-      <c r="N285" s="29"/>
+      <c r="M285" s="37"/>
+      <c r="N285" s="37"/>
       <c r="O285" s="24"/>
       <c r="P285" s="24"/>
       <c r="Q285" s="24"/>
@@ -18570,7 +18569,7 @@
       <c r="AG285" s="1"/>
       <c r="AH285" s="1"/>
     </row>
-    <row r="286" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="286" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A286" s="15" t="s">
         <v>308</v>
       </c>
@@ -18602,8 +18601,8 @@
       <c r="J286" s="24"/>
       <c r="K286" s="24"/>
       <c r="L286" s="24"/>
-      <c r="M286" s="29"/>
-      <c r="N286" s="29"/>
+      <c r="M286" s="37"/>
+      <c r="N286" s="37"/>
       <c r="O286" s="24"/>
       <c r="P286" s="24"/>
       <c r="Q286" s="24"/>
@@ -18628,7 +18627,7 @@
       <c r="AG286" s="1"/>
       <c r="AH286" s="1"/>
     </row>
-    <row r="287" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="287" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A287" s="15" t="s">
         <v>309</v>
       </c>
@@ -18660,8 +18659,8 @@
       <c r="J287" s="24"/>
       <c r="K287" s="24"/>
       <c r="L287" s="24"/>
-      <c r="M287" s="29"/>
-      <c r="N287" s="29"/>
+      <c r="M287" s="37"/>
+      <c r="N287" s="37"/>
       <c r="O287" s="24"/>
       <c r="P287" s="24"/>
       <c r="Q287" s="24"/>
@@ -18686,7 +18685,7 @@
       <c r="AG287" s="1"/>
       <c r="AH287" s="1"/>
     </row>
-    <row r="288" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="288" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A288" s="15" t="s">
         <v>310</v>
       </c>
@@ -18718,8 +18717,8 @@
       <c r="J288" s="24"/>
       <c r="K288" s="24"/>
       <c r="L288" s="24"/>
-      <c r="M288" s="29"/>
-      <c r="N288" s="29"/>
+      <c r="M288" s="37"/>
+      <c r="N288" s="37"/>
       <c r="O288" s="24"/>
       <c r="P288" s="24"/>
       <c r="Q288" s="24"/>
@@ -18744,7 +18743,7 @@
       <c r="AG288" s="1"/>
       <c r="AH288" s="1"/>
     </row>
-    <row r="289" spans="1:34" ht="16.5" hidden="1" customHeight="1" thickBot="1">
+    <row r="289" spans="1:34" ht="16.5" customHeight="1" thickBot="1">
       <c r="A289" s="15" t="s">
         <v>311</v>
       </c>
@@ -18776,8 +18775,8 @@
       <c r="J289" s="25"/>
       <c r="K289" s="25"/>
       <c r="L289" s="25"/>
-      <c r="M289" s="30"/>
-      <c r="N289" s="30"/>
+      <c r="M289" s="38"/>
+      <c r="N289" s="38"/>
       <c r="O289" s="25"/>
       <c r="P289" s="25"/>
       <c r="Q289" s="25"/>
@@ -26509,14 +26508,184 @@
     <row r="994" ht="15.75" customHeight="1"/>
     <row r="995" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:S289">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="도시가스(LNG)"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:S289"/>
   <mergeCells count="200">
+    <mergeCell ref="P230:P241"/>
+    <mergeCell ref="Q230:Q241"/>
+    <mergeCell ref="R230:R241"/>
+    <mergeCell ref="J230:J241"/>
+    <mergeCell ref="K230:K241"/>
+    <mergeCell ref="L230:L241"/>
+    <mergeCell ref="M230:M241"/>
+    <mergeCell ref="N230:N241"/>
+    <mergeCell ref="O230:O241"/>
+    <mergeCell ref="P218:P229"/>
+    <mergeCell ref="Q218:Q229"/>
+    <mergeCell ref="R218:R229"/>
+    <mergeCell ref="J218:J229"/>
+    <mergeCell ref="K218:K229"/>
+    <mergeCell ref="L218:L229"/>
+    <mergeCell ref="M218:M229"/>
+    <mergeCell ref="N218:N229"/>
+    <mergeCell ref="O218:O229"/>
+    <mergeCell ref="P206:P217"/>
+    <mergeCell ref="Q206:Q217"/>
+    <mergeCell ref="R206:R217"/>
+    <mergeCell ref="J206:J217"/>
+    <mergeCell ref="K206:K217"/>
+    <mergeCell ref="L206:L217"/>
+    <mergeCell ref="M206:M217"/>
+    <mergeCell ref="N206:N217"/>
+    <mergeCell ref="O206:O217"/>
+    <mergeCell ref="P194:P205"/>
+    <mergeCell ref="Q194:Q205"/>
+    <mergeCell ref="R194:R205"/>
+    <mergeCell ref="J194:J205"/>
+    <mergeCell ref="K194:K205"/>
+    <mergeCell ref="L194:L205"/>
+    <mergeCell ref="M194:M205"/>
+    <mergeCell ref="N194:N205"/>
+    <mergeCell ref="O194:O205"/>
+    <mergeCell ref="L170:L181"/>
+    <mergeCell ref="M170:M181"/>
+    <mergeCell ref="N170:N181"/>
+    <mergeCell ref="O170:O181"/>
+    <mergeCell ref="P170:R181"/>
+    <mergeCell ref="J182:J193"/>
+    <mergeCell ref="K182:K193"/>
+    <mergeCell ref="L182:L193"/>
+    <mergeCell ref="M182:M193"/>
+    <mergeCell ref="N182:N193"/>
+    <mergeCell ref="O182:O193"/>
+    <mergeCell ref="P182:R193"/>
+    <mergeCell ref="J98:J109"/>
+    <mergeCell ref="K98:K109"/>
+    <mergeCell ref="L98:L109"/>
+    <mergeCell ref="M98:M109"/>
+    <mergeCell ref="N98:N109"/>
+    <mergeCell ref="O98:O109"/>
+    <mergeCell ref="P98:R109"/>
+    <mergeCell ref="J110:J121"/>
+    <mergeCell ref="K110:K121"/>
+    <mergeCell ref="L110:L121"/>
+    <mergeCell ref="M110:M121"/>
+    <mergeCell ref="N110:N121"/>
+    <mergeCell ref="O110:O121"/>
+    <mergeCell ref="P110:R121"/>
+    <mergeCell ref="P278:P289"/>
+    <mergeCell ref="Q278:Q289"/>
+    <mergeCell ref="R278:R289"/>
+    <mergeCell ref="J278:J289"/>
+    <mergeCell ref="K278:K289"/>
+    <mergeCell ref="L278:L289"/>
+    <mergeCell ref="M278:M289"/>
+    <mergeCell ref="N278:N289"/>
+    <mergeCell ref="O278:O289"/>
+    <mergeCell ref="J26:J37"/>
+    <mergeCell ref="K26:K37"/>
+    <mergeCell ref="L26:L37"/>
+    <mergeCell ref="M26:M37"/>
+    <mergeCell ref="N26:N37"/>
+    <mergeCell ref="O26:O37"/>
+    <mergeCell ref="P26:R37"/>
+    <mergeCell ref="J38:J49"/>
+    <mergeCell ref="K38:K49"/>
+    <mergeCell ref="L38:L49"/>
+    <mergeCell ref="M38:M49"/>
+    <mergeCell ref="N38:N49"/>
+    <mergeCell ref="O38:O49"/>
+    <mergeCell ref="P38:R49"/>
+    <mergeCell ref="P14:P25"/>
+    <mergeCell ref="Q14:Q25"/>
+    <mergeCell ref="R14:R25"/>
+    <mergeCell ref="J14:J25"/>
+    <mergeCell ref="K14:K25"/>
+    <mergeCell ref="L14:L25"/>
+    <mergeCell ref="M14:M25"/>
+    <mergeCell ref="N14:N25"/>
+    <mergeCell ref="O14:O25"/>
+    <mergeCell ref="P2:P13"/>
+    <mergeCell ref="Q2:Q13"/>
+    <mergeCell ref="R2:R13"/>
+    <mergeCell ref="J2:J13"/>
+    <mergeCell ref="K2:K13"/>
+    <mergeCell ref="L2:L13"/>
+    <mergeCell ref="M2:M13"/>
+    <mergeCell ref="N2:N13"/>
+    <mergeCell ref="O2:O13"/>
+    <mergeCell ref="P266:P277"/>
+    <mergeCell ref="Q266:Q277"/>
+    <mergeCell ref="R266:R277"/>
+    <mergeCell ref="J266:J277"/>
+    <mergeCell ref="K266:K277"/>
+    <mergeCell ref="L266:L277"/>
+    <mergeCell ref="M266:M277"/>
+    <mergeCell ref="N266:N277"/>
+    <mergeCell ref="O266:O277"/>
+    <mergeCell ref="Q146:Q157"/>
+    <mergeCell ref="R146:R157"/>
+    <mergeCell ref="J146:J157"/>
+    <mergeCell ref="K146:K157"/>
+    <mergeCell ref="L146:L157"/>
+    <mergeCell ref="M146:M157"/>
+    <mergeCell ref="N146:N157"/>
+    <mergeCell ref="O146:O157"/>
+    <mergeCell ref="L254:L265"/>
+    <mergeCell ref="M254:M265"/>
+    <mergeCell ref="N254:N265"/>
+    <mergeCell ref="O254:O265"/>
+    <mergeCell ref="P254:R265"/>
+    <mergeCell ref="P158:P169"/>
+    <mergeCell ref="Q158:Q169"/>
+    <mergeCell ref="R158:R169"/>
+    <mergeCell ref="J158:J169"/>
+    <mergeCell ref="K158:K169"/>
+    <mergeCell ref="L158:L169"/>
+    <mergeCell ref="M158:M169"/>
+    <mergeCell ref="N158:N169"/>
+    <mergeCell ref="O158:O169"/>
+    <mergeCell ref="J170:J181"/>
+    <mergeCell ref="K170:K181"/>
+    <mergeCell ref="Q122:Q133"/>
+    <mergeCell ref="R122:R133"/>
+    <mergeCell ref="J122:J133"/>
+    <mergeCell ref="K122:K133"/>
+    <mergeCell ref="L122:L133"/>
+    <mergeCell ref="M122:M133"/>
+    <mergeCell ref="N122:N133"/>
+    <mergeCell ref="O122:O133"/>
+    <mergeCell ref="Q134:Q145"/>
+    <mergeCell ref="R134:R145"/>
+    <mergeCell ref="J134:J145"/>
+    <mergeCell ref="K134:K145"/>
+    <mergeCell ref="L134:L145"/>
+    <mergeCell ref="M134:M145"/>
+    <mergeCell ref="N134:N145"/>
+    <mergeCell ref="O134:O145"/>
+    <mergeCell ref="J254:J265"/>
+    <mergeCell ref="K254:K265"/>
+    <mergeCell ref="Q50:Q61"/>
+    <mergeCell ref="R50:R61"/>
+    <mergeCell ref="J50:J61"/>
+    <mergeCell ref="K50:K61"/>
+    <mergeCell ref="L50:L61"/>
+    <mergeCell ref="M50:M61"/>
+    <mergeCell ref="N50:N61"/>
+    <mergeCell ref="O50:O61"/>
+    <mergeCell ref="Q62:Q73"/>
+    <mergeCell ref="R62:R73"/>
+    <mergeCell ref="J62:J73"/>
+    <mergeCell ref="K62:K73"/>
+    <mergeCell ref="L62:L73"/>
+    <mergeCell ref="M62:M73"/>
+    <mergeCell ref="N62:N73"/>
+    <mergeCell ref="O62:O73"/>
+    <mergeCell ref="Q74:Q85"/>
+    <mergeCell ref="R74:R85"/>
+    <mergeCell ref="J74:J85"/>
+    <mergeCell ref="K74:K85"/>
+    <mergeCell ref="L74:L85"/>
+    <mergeCell ref="M74:M85"/>
     <mergeCell ref="P50:P61"/>
     <mergeCell ref="P62:P73"/>
     <mergeCell ref="P74:P85"/>
@@ -26541,182 +26710,6 @@
     <mergeCell ref="M86:M97"/>
     <mergeCell ref="N86:N97"/>
     <mergeCell ref="O86:O97"/>
-    <mergeCell ref="J254:J265"/>
-    <mergeCell ref="K254:K265"/>
-    <mergeCell ref="Q50:Q61"/>
-    <mergeCell ref="R50:R61"/>
-    <mergeCell ref="J50:J61"/>
-    <mergeCell ref="K50:K61"/>
-    <mergeCell ref="L50:L61"/>
-    <mergeCell ref="M50:M61"/>
-    <mergeCell ref="N50:N61"/>
-    <mergeCell ref="O50:O61"/>
-    <mergeCell ref="Q62:Q73"/>
-    <mergeCell ref="R62:R73"/>
-    <mergeCell ref="J62:J73"/>
-    <mergeCell ref="K62:K73"/>
-    <mergeCell ref="L62:L73"/>
-    <mergeCell ref="M62:M73"/>
-    <mergeCell ref="N62:N73"/>
-    <mergeCell ref="O62:O73"/>
-    <mergeCell ref="Q74:Q85"/>
-    <mergeCell ref="R74:R85"/>
-    <mergeCell ref="J74:J85"/>
-    <mergeCell ref="K74:K85"/>
-    <mergeCell ref="L74:L85"/>
-    <mergeCell ref="M74:M85"/>
-    <mergeCell ref="Q122:Q133"/>
-    <mergeCell ref="R122:R133"/>
-    <mergeCell ref="J122:J133"/>
-    <mergeCell ref="K122:K133"/>
-    <mergeCell ref="L122:L133"/>
-    <mergeCell ref="M122:M133"/>
-    <mergeCell ref="N122:N133"/>
-    <mergeCell ref="O122:O133"/>
-    <mergeCell ref="Q134:Q145"/>
-    <mergeCell ref="R134:R145"/>
-    <mergeCell ref="J134:J145"/>
-    <mergeCell ref="K134:K145"/>
-    <mergeCell ref="L134:L145"/>
-    <mergeCell ref="M134:M145"/>
-    <mergeCell ref="N134:N145"/>
-    <mergeCell ref="O134:O145"/>
-    <mergeCell ref="Q146:Q157"/>
-    <mergeCell ref="R146:R157"/>
-    <mergeCell ref="J146:J157"/>
-    <mergeCell ref="K146:K157"/>
-    <mergeCell ref="L146:L157"/>
-    <mergeCell ref="M146:M157"/>
-    <mergeCell ref="N146:N157"/>
-    <mergeCell ref="O146:O157"/>
-    <mergeCell ref="L254:L265"/>
-    <mergeCell ref="M254:M265"/>
-    <mergeCell ref="N254:N265"/>
-    <mergeCell ref="O254:O265"/>
-    <mergeCell ref="P254:R265"/>
-    <mergeCell ref="P158:P169"/>
-    <mergeCell ref="Q158:Q169"/>
-    <mergeCell ref="R158:R169"/>
-    <mergeCell ref="J158:J169"/>
-    <mergeCell ref="K158:K169"/>
-    <mergeCell ref="L158:L169"/>
-    <mergeCell ref="M158:M169"/>
-    <mergeCell ref="N158:N169"/>
-    <mergeCell ref="O158:O169"/>
-    <mergeCell ref="J170:J181"/>
-    <mergeCell ref="K170:K181"/>
-    <mergeCell ref="P266:P277"/>
-    <mergeCell ref="Q266:Q277"/>
-    <mergeCell ref="R266:R277"/>
-    <mergeCell ref="J266:J277"/>
-    <mergeCell ref="K266:K277"/>
-    <mergeCell ref="L266:L277"/>
-    <mergeCell ref="M266:M277"/>
-    <mergeCell ref="N266:N277"/>
-    <mergeCell ref="O266:O277"/>
-    <mergeCell ref="P2:P13"/>
-    <mergeCell ref="Q2:Q13"/>
-    <mergeCell ref="R2:R13"/>
-    <mergeCell ref="J2:J13"/>
-    <mergeCell ref="K2:K13"/>
-    <mergeCell ref="L2:L13"/>
-    <mergeCell ref="M2:M13"/>
-    <mergeCell ref="N2:N13"/>
-    <mergeCell ref="O2:O13"/>
-    <mergeCell ref="P14:P25"/>
-    <mergeCell ref="Q14:Q25"/>
-    <mergeCell ref="R14:R25"/>
-    <mergeCell ref="J14:J25"/>
-    <mergeCell ref="K14:K25"/>
-    <mergeCell ref="L14:L25"/>
-    <mergeCell ref="M14:M25"/>
-    <mergeCell ref="N14:N25"/>
-    <mergeCell ref="O14:O25"/>
-    <mergeCell ref="J26:J37"/>
-    <mergeCell ref="K26:K37"/>
-    <mergeCell ref="L26:L37"/>
-    <mergeCell ref="M26:M37"/>
-    <mergeCell ref="N26:N37"/>
-    <mergeCell ref="O26:O37"/>
-    <mergeCell ref="P26:R37"/>
-    <mergeCell ref="J38:J49"/>
-    <mergeCell ref="K38:K49"/>
-    <mergeCell ref="L38:L49"/>
-    <mergeCell ref="M38:M49"/>
-    <mergeCell ref="N38:N49"/>
-    <mergeCell ref="O38:O49"/>
-    <mergeCell ref="P38:R49"/>
-    <mergeCell ref="P278:P289"/>
-    <mergeCell ref="Q278:Q289"/>
-    <mergeCell ref="R278:R289"/>
-    <mergeCell ref="J278:J289"/>
-    <mergeCell ref="K278:K289"/>
-    <mergeCell ref="L278:L289"/>
-    <mergeCell ref="M278:M289"/>
-    <mergeCell ref="N278:N289"/>
-    <mergeCell ref="O278:O289"/>
-    <mergeCell ref="J98:J109"/>
-    <mergeCell ref="K98:K109"/>
-    <mergeCell ref="L98:L109"/>
-    <mergeCell ref="M98:M109"/>
-    <mergeCell ref="N98:N109"/>
-    <mergeCell ref="O98:O109"/>
-    <mergeCell ref="P98:R109"/>
-    <mergeCell ref="J110:J121"/>
-    <mergeCell ref="K110:K121"/>
-    <mergeCell ref="L110:L121"/>
-    <mergeCell ref="M110:M121"/>
-    <mergeCell ref="N110:N121"/>
-    <mergeCell ref="O110:O121"/>
-    <mergeCell ref="P110:R121"/>
-    <mergeCell ref="L170:L181"/>
-    <mergeCell ref="M170:M181"/>
-    <mergeCell ref="N170:N181"/>
-    <mergeCell ref="O170:O181"/>
-    <mergeCell ref="P170:R181"/>
-    <mergeCell ref="J182:J193"/>
-    <mergeCell ref="K182:K193"/>
-    <mergeCell ref="L182:L193"/>
-    <mergeCell ref="M182:M193"/>
-    <mergeCell ref="N182:N193"/>
-    <mergeCell ref="O182:O193"/>
-    <mergeCell ref="P182:R193"/>
-    <mergeCell ref="P194:P205"/>
-    <mergeCell ref="Q194:Q205"/>
-    <mergeCell ref="R194:R205"/>
-    <mergeCell ref="J194:J205"/>
-    <mergeCell ref="K194:K205"/>
-    <mergeCell ref="L194:L205"/>
-    <mergeCell ref="M194:M205"/>
-    <mergeCell ref="N194:N205"/>
-    <mergeCell ref="O194:O205"/>
-    <mergeCell ref="P206:P217"/>
-    <mergeCell ref="Q206:Q217"/>
-    <mergeCell ref="R206:R217"/>
-    <mergeCell ref="J206:J217"/>
-    <mergeCell ref="K206:K217"/>
-    <mergeCell ref="L206:L217"/>
-    <mergeCell ref="M206:M217"/>
-    <mergeCell ref="N206:N217"/>
-    <mergeCell ref="O206:O217"/>
-    <mergeCell ref="P218:P229"/>
-    <mergeCell ref="Q218:Q229"/>
-    <mergeCell ref="R218:R229"/>
-    <mergeCell ref="J218:J229"/>
-    <mergeCell ref="K218:K229"/>
-    <mergeCell ref="L218:L229"/>
-    <mergeCell ref="M218:M229"/>
-    <mergeCell ref="N218:N229"/>
-    <mergeCell ref="O218:O229"/>
-    <mergeCell ref="P230:P241"/>
-    <mergeCell ref="Q230:Q241"/>
-    <mergeCell ref="R230:R241"/>
-    <mergeCell ref="J230:J241"/>
-    <mergeCell ref="K230:K241"/>
-    <mergeCell ref="L230:L241"/>
-    <mergeCell ref="M230:M241"/>
-    <mergeCell ref="N230:N241"/>
-    <mergeCell ref="O230:O241"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
